--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F608"/>
+  <dimension ref="A1:F653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,15 +746,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>3</v>
@@ -768,18 +772,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -790,12 +798,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -812,12 +820,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,18 +842,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -856,12 +868,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -878,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -904,22 +912,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -930,19 +934,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
         <v>3</v>
@@ -1088,22 +1088,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1114,26 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1144,26 +1148,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1174,26 +1174,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1364,22 +1364,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalDEC</t>
+          <t>S&amp;P Global Services PMI FinalDEC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalDEC</t>
+          <t>S&amp;P Global Composite PMI FinalDEC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1712,22 +1712,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1738,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,26 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,18 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2124,26 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2154,14 +2154,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,22 +2180,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2202,22 +2210,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2228,26 +2228,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2332,15 +2332,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>3</v>
@@ -2354,22 +2358,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2424,18 +2424,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,22 +2450,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2472,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,19 +2498,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3054,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3084,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,26 +3252,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3282,22 +3278,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3308,10 +3308,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,12 +3330,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,26 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3584,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3644,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3682,14 +3682,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3700,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3734,18 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4036,26 +4036,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4066,26 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4096,26 +4092,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4156,26 +4152,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4186,22 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4212,26 +4212,26 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,17 +4322,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4348,19 +4348,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4374,17 +4370,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4400,12 +4396,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4422,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4444,15 +4440,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4582,26 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,26 +4608,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4642,26 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4672,26 +4664,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4702,26 +4686,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4732,26 +4708,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4762,24 +4730,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4792,18 +4752,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -4818,24 +4782,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4848,16 +4804,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4870,18 +4834,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4892,18 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4914,18 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4936,26 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4966,22 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,18 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -5014,18 +5014,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5762,18 +5762,18 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5806,18 +5806,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5968,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -6024,26 +6028,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,19 +6246,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6268,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6290,22 +6294,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6316,12 +6320,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,12 +6342,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,22 +6386,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6474,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6530,22 +6534,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/24</t>
+          <t>Baker Hughes Oil Rig CountJAN/24</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -6788,12 +6788,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/24</t>
+          <t>Baker Hughes Total Rigs CountJAN/24</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>576</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7204,18 +7204,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7230,26 +7230,26 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276">
@@ -7260,22 +7260,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7290,18 +7286,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7316,22 +7312,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -7816,18 +7816,22 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299">
@@ -7838,18 +7842,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.128M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7860,12 +7868,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7882,19 +7890,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7908,15 +7912,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7930,12 +7938,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7952,12 +7960,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7974,22 +7982,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.326M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8000,22 +8004,18 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307">
@@ -8096,22 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -8122,22 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8148,26 +8156,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8178,18 +8186,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8204,12 +8216,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -8230,22 +8242,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8260,26 +8268,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8290,26 +8298,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -8320,26 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8542,26 +8542,14 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,26 +8560,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
           <t>0.7%</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,18 +8590,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8628,26 +8620,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8658,18 +8650,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -8684,26 +8680,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8714,26 +8710,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8744,14 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+          <t>Personal Spending MoMDEC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8762,26 +8766,26 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F335" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -8792,7 +8796,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -8800,11 +8804,7 @@
           <t>0.9%</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8930,22 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,18 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8986,22 +8990,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,18 +9498,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,18 +9542,18 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="368">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9820,18 +9824,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9846,18 +9850,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9872,26 +9876,22 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -9902,18 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -9928,22 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9976,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9998,18 +9998,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.16M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -10020,22 +10024,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,18 +10090,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10112,19 +10116,15 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>3</v>
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10432,14 +10432,14 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
@@ -10891,11 +10891,11 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -10906,14 +10906,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,14 +10932,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,14 +10954,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10972,22 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -10998,14 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11020,18 +11024,14 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,14 +11046,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11068,18 +11068,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11094,22 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,18 +11264,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -11286,18 +11286,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11308,22 +11312,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11334,22 +11338,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11360,18 +11360,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -11382,18 +11386,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11404,22 +11412,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11430,18 +11434,14 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11456,14 +11456,14 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11701,12 +11701,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2025-02-17 20:00:00+05:30</t>
+          <t>2025-02-15 01:30:00+05:30</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Fed Harker Speech</t>
+          <t>Fed Logan Speech</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11737,12 +11737,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2025-02-17 20:50:00+05:30</t>
+          <t>2025-02-17 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Harker Speech</t>
         </is>
       </c>
       <c r="C467" t="inlineStr"/>
@@ -11755,12 +11755,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2025-02-18 04:30:00+05:30</t>
+          <t>2025-02-17 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C468" t="inlineStr"/>
@@ -11773,12 +11773,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2025-02-18 19:00:00+05:30</t>
+          <t>2025-02-17 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C469" t="inlineStr"/>
@@ -11791,25 +11791,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2025-02-18 19:00:00+05:30</t>
+          <t>2025-02-18 04:30:00+05:30</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C470" t="inlineStr"/>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E470" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="D470" t="inlineStr"/>
+      <c r="E470" t="inlineStr"/>
       <c r="F470" t="n">
         <v>2</v>
       </c>
@@ -11817,25 +11809,17 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2025-02-18 20:30:00+05:30</t>
+          <t>2025-02-18 04:30:00+05:30</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexFEB</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C471" t="inlineStr"/>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="D471" t="inlineStr"/>
+      <c r="E471" t="inlineStr"/>
       <c r="F471" t="n">
         <v>2</v>
       </c>
@@ -11843,17 +11827,25 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2025-02-18 20:30:00+05:30</t>
+          <t>2025-02-18 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexFEB</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
-      <c r="E472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F472" t="n">
         <v>2</v>
       </c>
@@ -11861,17 +11853,25 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2025-02-18 20:50:00+05:30</t>
+          <t>2025-02-18 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
-      <c r="E473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F473" t="n">
         <v>2</v>
       </c>
@@ -11879,84 +11879,92 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2025-02-18 22:00:00+05:30</t>
+          <t>2025-02-18 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
-      <c r="E474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="F474" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2025-02-18 22:00:00+05:30</t>
+          <t>2025-02-18 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr"/>
       <c r="F475" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2025-02-18 22:00:00+05:30</t>
+          <t>2025-02-18 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr"/>
       <c r="F476" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2025-02-18 22:00:00+05:30</t>
+          <t>2025-02-18 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr"/>
       <c r="F477" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2025-02-18 22:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -11969,12 +11977,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2025-02-18 22:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -11987,30 +11995,30 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2025-02-18 23:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2025-02-18 23:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -12023,12 +12031,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C482" t="inlineStr"/>
@@ -12041,12 +12049,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C483" t="inlineStr"/>
@@ -12059,70 +12067,66 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
@@ -12135,12 +12139,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
@@ -12153,12 +12157,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
@@ -12171,12 +12175,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -12189,30 +12193,30 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12225,12 +12229,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -12243,19 +12247,23 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12266,7 +12274,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12284,7 +12292,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -12302,83 +12310,79 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
+      <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr"/>
       <c r="F500" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -12391,71 +12395,55 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
-      <c r="E503" t="inlineStr">
-        <is>
-          <t>1.35M</t>
-        </is>
-      </c>
+      <c r="D503" t="inlineStr"/>
+      <c r="E503" t="inlineStr"/>
       <c r="F503" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
-      <c r="E504" t="inlineStr">
-        <is>
-          <t>1.47M</t>
-        </is>
-      </c>
+      <c r="D504" t="inlineStr"/>
+      <c r="E504" t="inlineStr"/>
       <c r="F504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -12466,249 +12454,293 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2025-02-19 19:25:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/15</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
-      <c r="E506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>1.35M</t>
+        </is>
+      </c>
       <c r="F506" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2025-02-19 19:25:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/15</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
       <c r="D507" t="inlineStr"/>
-      <c r="E507" t="inlineStr"/>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F507" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2025-02-19 21:00:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
-      <c r="E508" t="inlineStr"/>
+      <c r="D508" t="inlineStr"/>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-9.0%</t>
+        </is>
+      </c>
       <c r="F508" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2025-02-19 22:00:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
-      <c r="E509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>1.35M</t>
+        </is>
+      </c>
       <c r="F509" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2025-02-19 22:00:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr"/>
       <c r="F510" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2025-02-19 23:30:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
-      <c r="E511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>1.47M</t>
+        </is>
+      </c>
       <c r="F511" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2025-02-19 23:30:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr"/>
-      <c r="E512" t="inlineStr"/>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-9.0%</t>
+        </is>
+      </c>
       <c r="F512" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2025-02-20 00:30:00+05:30</t>
+          <t>2025-02-19 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>FOMC Minutes</t>
+          <t>Redbook YoYFEB/15</t>
         </is>
       </c>
       <c r="C513" t="inlineStr"/>
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr"/>
       <c r="F513" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2025-02-20 00:30:00+05:30</t>
+          <t>2025-02-19 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>FOMC Minutes</t>
+          <t>Redbook YoYFEB/15</t>
         </is>
       </c>
       <c r="C514" t="inlineStr"/>
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr"/>
       <c r="F514" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2025-02-20 03:00:00+05:30</t>
+          <t>2025-02-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/14</t>
+          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr"/>
       <c r="F515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2025-02-20 03:00:00+05:30</t>
+          <t>2025-02-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/14</t>
+          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr"/>
       <c r="F516" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2025-02-20 03:30:00+05:30</t>
+          <t>2025-02-19 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr"/>
       <c r="F517" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
@@ -12721,12 +12753,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
@@ -12739,115 +12771,107 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr"/>
       <c r="F520" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-20 00:30:00+05:30</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr"/>
       <c r="F521" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-20 00:30:00+05:30</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr"/>
       <c r="F522" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-20 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>API Crude Oil Stock ChangeFEB/14</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
       <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr"/>
       <c r="F523" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-20 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>API Crude Oil Stock ChangeFEB/14</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
       <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr"/>
       <c r="F524" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-20 03:30:00+05:30</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C525" t="inlineStr"/>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E525" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D525" t="inlineStr"/>
+      <c r="E525" t="inlineStr"/>
       <c r="F525" t="n">
         <v>2</v>
       </c>
@@ -12855,25 +12879,17 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-20 03:30:00+05:30</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr"/>
       <c r="F526" t="n">
         <v>2</v>
       </c>
@@ -12886,14 +12902,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F527" t="n">
@@ -12908,18 +12924,22 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F528" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -12930,12 +12950,16 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
-      <c r="E529" t="inlineStr"/>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F529" t="n">
         <v>3</v>
       </c>
@@ -12948,7 +12972,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -12966,7 +12990,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -12984,7 +13008,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13002,7 +13026,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13020,7 +13044,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -13038,30 +13062,46 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2025-02-20 20:05:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
         <v>2</v>
       </c>
@@ -13069,35 +13109,39 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2025-02-20 20:05:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2025-02-20 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13105,25 +13149,17 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2025-02-20 20:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13131,12 +13167,12 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2025-02-20 21:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -13149,12 +13185,12 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2025-02-20 21:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13167,12 +13203,12 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2025-02-20 22:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13185,35 +13221,47 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2025-02-20 22:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr"/>
-      <c r="E543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2025-02-20 22:00:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
-      <c r="E544" t="inlineStr"/>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F544" t="n">
         <v>3</v>
       </c>
@@ -13221,30 +13269,30 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2025-02-20 22:00:00+05:30</t>
+          <t>2025-02-20 20:05:00+05:30</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr"/>
       <c r="F545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 20:05:00+05:30</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -13257,17 +13305,25 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr"/>
-      <c r="E547" t="inlineStr"/>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="F547" t="n">
         <v>3</v>
       </c>
@@ -13275,17 +13331,25 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
-      <c r="E548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="F548" t="n">
         <v>3</v>
       </c>
@@ -13293,12 +13357,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
@@ -13311,12 +13375,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -13329,12 +13393,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
@@ -13347,12 +13411,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13365,30 +13429,30 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr"/>
       <c r="F553" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
@@ -13424,14 +13488,14 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -13442,14 +13506,14 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="558">
@@ -13460,7 +13524,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13478,7 +13542,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13496,7 +13560,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13514,14 +13578,14 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562">
@@ -13532,14 +13596,14 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr"/>
       <c r="F562" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="563">
@@ -13550,14 +13614,14 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="564">
@@ -13586,7 +13650,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13604,7 +13668,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13640,7 +13704,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -13653,84 +13717,84 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2025-02-20 22:35:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2025-02-20 23:30:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2025-02-20 23:30:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2025-02-21 01:00:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr"/>
       <c r="F572" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2025-02-21 03:00:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/19</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -13743,12 +13807,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2025-02-21 03:00:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/19</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -13761,39 +13825,35 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2025-02-21 03:30:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr"/>
       <c r="F575" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2025-02-21 20:15:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
+      <c r="E576" t="inlineStr"/>
       <c r="F576" t="n">
         <v>2</v>
       </c>
@@ -13801,47 +13861,35 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2025-02-21 20:15:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
+      <c r="E577" t="inlineStr"/>
       <c r="F577" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2025-02-21 20:15:00+05:30</t>
+          <t>2025-02-20 22:35:00+05:30</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="E578" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="inlineStr"/>
       <c r="F578" t="n">
         <v>2</v>
       </c>
@@ -13849,51 +13897,35 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 22:35:00+05:30</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="E579" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="D579" t="inlineStr"/>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
-      <c r="E580" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D580" t="inlineStr"/>
+      <c r="E580" t="inlineStr"/>
       <c r="F580" t="n">
         <v>3</v>
       </c>
@@ -13901,25 +13933,17 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-20 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
-      <c r="E581" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D581" t="inlineStr"/>
+      <c r="E581" t="inlineStr"/>
       <c r="F581" t="n">
         <v>3</v>
       </c>
@@ -13927,112 +13951,84 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-21 01:00:00+05:30</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E582" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D582" t="inlineStr"/>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-21 01:00:00+05:30</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
-      <c r="E583" t="inlineStr">
-        <is>
-          <t>4.16M</t>
-        </is>
-      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-21 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Fed Balance SheetFEB/19</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr">
-        <is>
-          <t>-1.7%</t>
-        </is>
-      </c>
+      <c r="E584" t="inlineStr"/>
       <c r="F584" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-21 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Fed Balance SheetFEB/19</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
-      <c r="D585" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="E585" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D585" t="inlineStr"/>
+      <c r="E585" t="inlineStr"/>
       <c r="F585" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2025-02-21 22:00:00+05:30</t>
+          <t>2025-02-21 03:30:00+05:30</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
@@ -14045,53 +14041,61 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2025-02-21 23:30:00+05:30</t>
+          <t>2025-02-21 03:30:00+05:30</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr"/>
       <c r="F587" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2025-02-21 23:30:00+05:30</t>
+          <t>2025-02-21 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr"/>
-      <c r="E588" t="inlineStr"/>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="F588" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2025-02-24 19:00:00+05:30</t>
+          <t>2025-02-21 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Chicago Fed National Activity IndexJAN</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
-      <c r="E589" t="inlineStr"/>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F589" t="n">
         <v>2</v>
       </c>
@@ -14099,17 +14103,21 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2025-02-24 21:00:00+05:30</t>
+          <t>2025-02-21 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Dallas Fed Manufacturing IndexFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr"/>
-      <c r="E590" t="inlineStr"/>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>51.3</t>
+        </is>
+      </c>
       <c r="F590" t="n">
         <v>2</v>
       </c>
@@ -14117,71 +14125,99 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2025-02-24 22:00:00+05:30</t>
+          <t>2025-02-21 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
-      <c r="D591" t="inlineStr"/>
-      <c r="E591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F591" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2025-02-24 22:00:00+05:30</t>
+          <t>2025-02-21 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr"/>
-      <c r="E592" t="inlineStr"/>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F592" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2025-02-24 23:30:00+05:30</t>
+          <t>2025-02-21 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
-      <c r="D593" t="inlineStr"/>
-      <c r="E593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F593" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2025-02-25 19:25:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/22</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
-      <c r="D594" t="inlineStr"/>
-      <c r="E594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F594" t="n">
         <v>3</v>
       </c>
@@ -14189,17 +14225,25 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
-      <c r="D595" t="inlineStr"/>
-      <c r="E595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="F595" t="n">
         <v>3</v>
       </c>
@@ -14207,17 +14251,25 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr"/>
-      <c r="E596" t="inlineStr"/>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="F596" t="n">
         <v>3</v>
       </c>
@@ -14225,17 +14277,25 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
-      <c r="D597" t="inlineStr"/>
-      <c r="E597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="F597" t="n">
         <v>3</v>
       </c>
@@ -14243,19 +14303,23 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
-      <c r="D598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F598" t="n">
@@ -14265,53 +14329,73 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr"/>
-      <c r="E599" t="inlineStr"/>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2025-02-25 20:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
-      <c r="E600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>4.16M</t>
+        </is>
+      </c>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2025-02-25 20:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
-      <c r="D601" t="inlineStr"/>
-      <c r="E601" t="inlineStr"/>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="F601" t="n">
         <v>3</v>
       </c>
@@ -14319,17 +14403,25 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2025-02-25 20:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
-      <c r="E602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F602" t="n">
         <v>3</v>
       </c>
@@ -14337,53 +14429,73 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2025-02-25 20:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr"/>
-      <c r="E603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2025-02-25 21:00:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr"/>
-      <c r="E604" t="inlineStr"/>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2025-02-25 21:00:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
-      <c r="D605" t="inlineStr"/>
-      <c r="E605" t="inlineStr"/>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="F605" t="n">
         <v>3</v>
       </c>
@@ -14391,17 +14503,25 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2025-02-25 23:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
-      <c r="D606" t="inlineStr"/>
-      <c r="E606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="F606" t="n">
         <v>3</v>
       </c>
@@ -14409,30 +14529,38 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2025-02-25 23:30:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
-      <c r="D607" t="inlineStr"/>
-      <c r="E607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>4.16M</t>
+        </is>
+      </c>
       <c r="F607" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2025-02-26 03:00:00+05:30</t>
+          <t>2025-02-21 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/21</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -14442,6 +14570,824 @@
         <v>2</v>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2025-02-21 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Fed Jefferson Speech</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr"/>
+      <c r="D609" t="inlineStr"/>
+      <c r="E609" t="inlineStr"/>
+      <c r="F609" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2025-02-21 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr"/>
+      <c r="D610" t="inlineStr"/>
+      <c r="E610" t="inlineStr"/>
+      <c r="F610" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2025-02-21 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr"/>
+      <c r="D611" t="inlineStr"/>
+      <c r="E611" t="inlineStr"/>
+      <c r="F611" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2025-02-21 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr"/>
+      <c r="D612" t="inlineStr"/>
+      <c r="E612" t="inlineStr"/>
+      <c r="F612" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2025-02-21 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr"/>
+      <c r="D613" t="inlineStr"/>
+      <c r="E613" t="inlineStr"/>
+      <c r="F613" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2025-02-24 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Chicago Fed National Activity IndexJAN</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr"/>
+      <c r="D614" t="inlineStr"/>
+      <c r="E614" t="inlineStr"/>
+      <c r="F614" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2025-02-24 19:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Chicago Fed National Activity IndexJAN</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr"/>
+      <c r="D615" t="inlineStr"/>
+      <c r="E615" t="inlineStr"/>
+      <c r="F615" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2025-02-24 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Dallas Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr"/>
+      <c r="D616" t="inlineStr"/>
+      <c r="E616" t="inlineStr"/>
+      <c r="F616" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2025-02-24 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Dallas Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr"/>
+      <c r="D617" t="inlineStr"/>
+      <c r="E617" t="inlineStr"/>
+      <c r="F617" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2025-02-24 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr"/>
+      <c r="D618" t="inlineStr"/>
+      <c r="E618" t="inlineStr"/>
+      <c r="F618" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2025-02-24 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr"/>
+      <c r="D619" t="inlineStr"/>
+      <c r="E619" t="inlineStr"/>
+      <c r="F619" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2025-02-24 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr"/>
+      <c r="D620" t="inlineStr"/>
+      <c r="E620" t="inlineStr"/>
+      <c r="F620" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2025-02-24 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr"/>
+      <c r="D621" t="inlineStr"/>
+      <c r="E621" t="inlineStr"/>
+      <c r="F621" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2025-02-24 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>2-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr"/>
+      <c r="D622" t="inlineStr"/>
+      <c r="E622" t="inlineStr"/>
+      <c r="F622" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2025-02-24 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>2-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr"/>
+      <c r="D623" t="inlineStr"/>
+      <c r="E623" t="inlineStr"/>
+      <c r="F623" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:25:00+05:30</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Redbook YoYFEB/22</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr"/>
+      <c r="D624" t="inlineStr"/>
+      <c r="E624" t="inlineStr"/>
+      <c r="F624" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:25:00+05:30</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Redbook YoYFEB/22</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr"/>
+      <c r="D625" t="inlineStr"/>
+      <c r="E625" t="inlineStr"/>
+      <c r="F625" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr"/>
+      <c r="D626" t="inlineStr"/>
+      <c r="E626" t="inlineStr"/>
+      <c r="F626" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr"/>
+      <c r="D627" t="inlineStr"/>
+      <c r="E627" t="inlineStr"/>
+      <c r="F627" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr"/>
+      <c r="D628" t="inlineStr"/>
+      <c r="E628" t="inlineStr"/>
+      <c r="F628" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr"/>
+      <c r="D629" t="inlineStr"/>
+      <c r="E629" t="inlineStr"/>
+      <c r="F629" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>House Price IndexDEC</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr"/>
+      <c r="D630" t="inlineStr"/>
+      <c r="E630" t="inlineStr"/>
+      <c r="F630" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr"/>
+      <c r="D631" t="inlineStr"/>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F631" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>House Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr"/>
+      <c r="D632" t="inlineStr"/>
+      <c r="E632" t="inlineStr"/>
+      <c r="F632" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr"/>
+      <c r="D633" t="inlineStr"/>
+      <c r="E633" t="inlineStr"/>
+      <c r="F633" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr"/>
+      <c r="D634" t="inlineStr"/>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="F634" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2025-02-25 19:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>House Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr"/>
+      <c r="D635" t="inlineStr"/>
+      <c r="E635" t="inlineStr"/>
+      <c r="F635" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr"/>
+      <c r="D636" t="inlineStr"/>
+      <c r="E636" t="inlineStr"/>
+      <c r="F636" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr"/>
+      <c r="D637" t="inlineStr"/>
+      <c r="E637" t="inlineStr"/>
+      <c r="F637" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr"/>
+      <c r="D638" t="inlineStr"/>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>CB Consumer ConfidenceFEB</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr"/>
+      <c r="D639" t="inlineStr"/>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr"/>
+      <c r="D640" t="inlineStr"/>
+      <c r="E640" t="inlineStr"/>
+      <c r="F640" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr"/>
+      <c r="D641" t="inlineStr"/>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr"/>
+      <c r="D642" t="inlineStr"/>
+      <c r="E642" t="inlineStr"/>
+      <c r="F642" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2025-02-25 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr"/>
+      <c r="D643" t="inlineStr"/>
+      <c r="E643" t="inlineStr"/>
+      <c r="F643" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr"/>
+      <c r="D644" t="inlineStr"/>
+      <c r="E644" t="inlineStr"/>
+      <c r="F644" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr"/>
+      <c r="D645" t="inlineStr"/>
+      <c r="E645" t="inlineStr"/>
+      <c r="F645" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr"/>
+      <c r="D646" t="inlineStr"/>
+      <c r="E646" t="inlineStr"/>
+      <c r="F646" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2025-02-25 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Dallas Fed Services IndexFEB</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr"/>
+      <c r="D647" t="inlineStr"/>
+      <c r="E647" t="inlineStr"/>
+      <c r="F647" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Money SupplyJAN</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr"/>
+      <c r="D648" t="inlineStr"/>
+      <c r="E648" t="inlineStr"/>
+      <c r="F648" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>5-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr"/>
+      <c r="D649" t="inlineStr"/>
+      <c r="E649" t="inlineStr"/>
+      <c r="F649" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Money SupplyJAN</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr"/>
+      <c r="D650" t="inlineStr"/>
+      <c r="E650" t="inlineStr"/>
+      <c r="F650" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2025-02-25 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>5-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr"/>
+      <c r="D651" t="inlineStr"/>
+      <c r="E651" t="inlineStr"/>
+      <c r="F651" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2025-02-26 03:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr"/>
+      <c r="D652" t="inlineStr"/>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2025-02-26 03:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr"/>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" t="inlineStr"/>
+      <c r="F653" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F653"/>
+  <dimension ref="A1:F652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,19 +746,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>3</v>
@@ -772,18 +768,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -794,12 +794,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -816,18 +816,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -838,22 +842,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -864,12 +864,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -886,22 +886,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -912,15 +908,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.099M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>3</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1088,26 +1088,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1118,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1144,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1174,26 +1178,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1364,22 +1364,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalDEC</t>
+          <t>S&amp;P Global Services PMI FinalDEC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalDEC</t>
+          <t>S&amp;P Global Composite PMI FinalDEC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1712,22 +1712,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1738,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,26 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,18 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2124,26 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2154,14 +2154,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,22 +2180,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2202,22 +2210,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2228,26 +2228,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2332,15 +2332,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>3</v>
@@ -2354,22 +2358,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2402,18 +2402,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2424,22 +2428,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2472,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,19 +2498,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2946,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -3002,22 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,22 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3054,26 +3062,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3084,26 +3092,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,22 +3174,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3200,18 +3204,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3278,26 +3282,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3308,10 +3308,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,12 +3330,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3596,14 +3596,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,18 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3674,26 +3674,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3704,18 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,26 +3734,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -4036,26 +4036,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4066,26 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4096,26 +4092,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4156,26 +4152,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4186,22 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4212,26 +4212,26 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,17 +4322,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4348,19 +4348,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4374,17 +4370,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4400,12 +4396,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4422,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4444,15 +4440,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4582,18 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4608,26 +4608,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4638,26 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4668,26 +4664,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4698,26 +4686,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4728,26 +4708,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4758,24 +4730,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4788,24 +4752,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4818,18 +4774,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -4840,16 +4804,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4862,18 +4834,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4884,18 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4906,18 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4928,26 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4958,22 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4984,22 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,18 +5010,22 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5762,18 +5762,18 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218">
@@ -5784,18 +5784,18 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5968,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -6024,26 +6028,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6264,22 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239">
@@ -6290,19 +6294,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
         <v>3</v>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,22 +6382,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6408,18 +6404,22 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
@@ -6474,18 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6500,22 +6504,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6530,22 +6534,18 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7066,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7096,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,22 +7122,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,18 +7664,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,15 +7860,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7882,18 +7886,22 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -7904,17 +7912,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -7930,22 +7938,18 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -7956,19 +7960,15 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>3</v>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,12 +8096,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -8122,26 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8152,26 +8148,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8182,18 +8178,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8208,26 +8208,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
@@ -8238,22 +8234,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,22 +8260,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -8294,26 +8290,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -8324,22 +8320,26 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8572,15 +8572,19 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8598,18 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8624,26 +8632,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8662,14 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,14 +8680,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+          <t>Core PCE Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8702,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8732,26 +8740,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8762,22 +8766,18 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -8960,18 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -8986,26 +8990,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9016,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>8M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9288,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,18 +9318,18 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F357" t="n">
@@ -9616,14 +9616,26 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
-      <c r="D370" t="inlineStr"/>
-      <c r="E370" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
@@ -9634,18 +9646,18 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F371" t="n">
@@ -9660,22 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9686,22 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,18 +9928,22 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383">
@@ -9950,18 +9954,22 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
@@ -9972,12 +9980,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,19 +10002,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10020,12 +10024,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10042,15 +10046,19 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10064,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10090,12 +10094,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10112,22 +10116,18 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
@@ -10494,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10520,18 +10520,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -10542,7 +10546,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
@@ -10553,7 +10557,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10568,22 +10572,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -10594,22 +10598,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="414">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10880,18 +10880,18 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10906,18 +10906,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="430">
@@ -10928,18 +10932,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -10950,14 +10958,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10972,22 +10980,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -10998,14 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11020,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -11042,18 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11068,22 +11072,18 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11094,22 +11094,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,22 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -11290,18 +11290,14 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F447" t="n">
@@ -11316,14 +11312,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -11338,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11364,14 +11356,14 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F450" t="n">
@@ -11386,18 +11378,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11408,22 +11404,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11434,18 +11430,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -11456,18 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11701,12 +11701,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2025-02-15 01:30:00+05:30</t>
+          <t>2025-02-17 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Fed Logan Speech</t>
+          <t>Fed Harker Speech</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -11737,12 +11737,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2025-02-17 20:00:00+05:30</t>
+          <t>2025-02-17 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Fed Harker Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C467" t="inlineStr"/>
@@ -11773,12 +11773,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2025-02-17 20:50:00+05:30</t>
+          <t>2025-02-18 04:30:00+05:30</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Waller Speech</t>
         </is>
       </c>
       <c r="C469" t="inlineStr"/>
@@ -11809,17 +11809,25 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2025-02-18 04:30:00+05:30</t>
+          <t>2025-02-18 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
+          <t>NY Empire State Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C471" t="inlineStr"/>
-      <c r="D471" t="inlineStr"/>
-      <c r="E471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F471" t="n">
         <v>2</v>
       </c>
@@ -11853,25 +11861,17 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2025-02-18 19:00:00+05:30</t>
+          <t>2025-02-18 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexFEB</t>
+          <t>NAHB Housing Market IndexFEB</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="D473" t="inlineStr"/>
+      <c r="E473" t="inlineStr"/>
       <c r="F473" t="n">
         <v>2</v>
       </c>
@@ -11905,12 +11905,12 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2025-02-18 20:30:00+05:30</t>
+          <t>2025-02-18 20:50:00+05:30</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexFEB</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
@@ -11941,19 +11941,19 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2025-02-18 20:50:00+05:30</t>
+          <t>2025-02-18 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr"/>
       <c r="F477" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -12031,12 +12031,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2025-02-18 22:00:00+05:30</t>
+          <t>2025-02-18 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C482" t="inlineStr"/>
@@ -12067,19 +12067,19 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2025-02-18 22:30:00+05:30</t>
+          <t>2025-02-18 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="485">
@@ -12090,14 +12090,14 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="486">
@@ -12139,12 +12139,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2025-02-18 23:30:00+05:30</t>
+          <t>2025-02-19 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
@@ -12202,14 +12202,18 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr"/>
       <c r="F491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -12220,7 +12224,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -12238,7 +12242,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -12251,20 +12255,16 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2025-02-19 02:30:00+05:30</t>
+          <t>2025-02-19 17:30:00+05:30</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
         <v>2</v>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -12350,14 +12350,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -12386,14 +12386,14 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -12435,19 +12435,27 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2025-02-19 17:30:00+05:30</t>
+          <t>2025-02-19 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr"/>
-      <c r="E504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>1.35M</t>
+        </is>
+      </c>
       <c r="F504" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
@@ -12458,18 +12466,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12484,22 +12492,14 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
-      <c r="E506" t="inlineStr">
-        <is>
-          <t>1.35M</t>
-        </is>
-      </c>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="inlineStr"/>
       <c r="F506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="507">
@@ -12510,18 +12510,22 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F507" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -12559,7 +12563,11 @@
       </c>
       <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr"/>
-      <c r="E509" t="inlineStr"/>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
       <c r="F509" t="n">
         <v>2</v>
       </c>
@@ -12572,22 +12580,18 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="511">
@@ -12619,23 +12623,19 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2025-02-19 19:00:00+05:30</t>
+          <t>2025-02-19 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Redbook YoYFEB/15</t>
         </is>
       </c>
       <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr"/>
-      <c r="E512" t="inlineStr">
-        <is>
-          <t>-9.0%</t>
-        </is>
-      </c>
+      <c r="E512" t="inlineStr"/>
       <c r="F512" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="513">
@@ -12659,16 +12659,20 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2025-02-19 19:25:00+05:30</t>
+          <t>2025-02-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/15</t>
+          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
         </is>
       </c>
       <c r="C514" t="inlineStr"/>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>$50 million</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr"/>
       <c r="F514" t="n">
         <v>3</v>
@@ -12699,20 +12703,16 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2025-02-19 21:00:00+05:30</t>
+          <t>2025-02-19 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>NY Fed Treasury Purchases 22.5 to 30 yrs</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>$50 million</t>
-        </is>
-      </c>
+      <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr"/>
       <c r="F516" t="n">
         <v>3</v>
@@ -12739,12 +12739,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2025-02-19 22:00:00+05:30</t>
+          <t>2025-02-19 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
@@ -12775,19 +12775,19 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2025-02-19 23:30:00+05:30</t>
+          <t>2025-02-20 00:30:00+05:30</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr"/>
       <c r="F520" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="521">
@@ -12811,19 +12811,19 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2025-02-20 00:30:00+05:30</t>
+          <t>2025-02-20 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>FOMC Minutes</t>
+          <t>API Crude Oil Stock ChangeFEB/14</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr"/>
       <c r="F522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="523">
@@ -12847,12 +12847,12 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2025-02-20 03:00:00+05:30</t>
+          <t>2025-02-20 03:30:00+05:30</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeFEB/14</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -12883,19 +12883,19 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2025-02-20 03:30:00+05:30</t>
+          <t>2025-02-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
       <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr"/>
       <c r="F526" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="527">
@@ -12906,16 +12906,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr"/>
-      <c r="E527" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
         <v>3</v>
       </c>
@@ -12928,22 +12924,14 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E528" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="inlineStr"/>
       <c r="F528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -12954,16 +12942,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
         <v>3</v>
       </c>
@@ -12976,14 +12960,22 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
-      <c r="D530" t="inlineStr"/>
-      <c r="E530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F530" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="531">
@@ -12994,14 +12986,22 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13012,12 +13012,16 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F532" t="n">
         <v>3</v>
       </c>
@@ -13030,7 +13034,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -13048,12 +13052,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F534" t="n">
         <v>3</v>
       </c>
@@ -13066,22 +13074,14 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13092,14 +13092,22 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F536" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -13110,22 +13118,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13136,22 +13136,14 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -13162,16 +13154,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13206,12 +13194,16 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr"/>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F541" t="n">
         <v>3</v>
       </c>
@@ -13224,14 +13216,22 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
-      <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr"/>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F542" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="543">
@@ -13255,19 +13255,19 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2025-02-20 19:00:00+05:30</t>
+          <t>2025-02-20 20:05:00+05:30</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr"/>
       <c r="F544" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="545">
@@ -13291,19 +13291,27 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2025-02-20 20:05:00+05:30</t>
+          <t>2025-02-20 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>CB Leading Index MoMJAN</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr"/>
-      <c r="E546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="F546" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="547">
@@ -13335,25 +13343,17 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2025-02-20 20:30:00+05:30</t>
+          <t>2025-02-20 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMJAN</t>
+          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E548" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="inlineStr"/>
       <c r="F548" t="n">
         <v>3</v>
       </c>
@@ -13379,12 +13379,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2025-02-20 21:00:00+05:30</t>
+          <t>2025-02-20 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeFEB/14</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -13451,12 +13451,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2025-02-20 22:00:00+05:30</t>
+          <t>2025-02-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13528,14 +13528,14 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13564,7 +13564,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13582,14 +13582,14 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13636,14 +13636,14 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr"/>
       <c r="F564" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="565">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13672,14 +13672,14 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="567">
@@ -13690,14 +13690,14 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="568">
@@ -13708,14 +13708,14 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="569">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
@@ -13744,14 +13744,14 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr"/>
       <c r="F570" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -13762,14 +13762,14 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="572">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
@@ -13798,14 +13798,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr"/>
       <c r="F573" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -13852,32 +13852,32 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr"/>
       <c r="E576" t="inlineStr"/>
       <c r="F576" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2025-02-20 22:30:00+05:30</t>
+          <t>2025-02-20 22:35:00+05:30</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr"/>
       <c r="E577" t="inlineStr"/>
       <c r="F577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="578">
@@ -13901,19 +13901,19 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2025-02-20 22:35:00+05:30</t>
+          <t>2025-02-20 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>30-Year TIPS Auction</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr"/>
       <c r="E579" t="inlineStr"/>
       <c r="F579" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="580">
@@ -13937,19 +13937,19 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2025-02-20 23:30:00+05:30</t>
+          <t>2025-02-21 01:00:00+05:30</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>30-Year TIPS Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C581" t="inlineStr"/>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr"/>
       <c r="F581" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="582">
@@ -13973,19 +13973,19 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2025-02-21 01:00:00+05:30</t>
+          <t>2025-02-21 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>Fed Balance SheetFEB/19</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr"/>
       <c r="F583" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="584">
@@ -14009,19 +14009,19 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2025-02-21 03:00:00+05:30</t>
+          <t>2025-02-21 03:30:00+05:30</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Fed Balance SheetFEB/19</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr"/>
       <c r="E585" t="inlineStr"/>
       <c r="F585" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="586">
@@ -14045,17 +14045,25 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2025-02-21 03:30:00+05:30</t>
+          <t>2025-02-21 20:15:00+05:30</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
-      <c r="E587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
       <c r="F587" t="n">
         <v>2</v>
       </c>
@@ -14112,11 +14120,15 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14134,15 +14146,11 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D591" t="inlineStr"/>
       <c r="E591" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14177,27 +14185,27 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2025-02-21 20:15:00+05:30</t>
+          <t>2025-02-21 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F593" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="594">
@@ -14208,22 +14216,18 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+      <c r="D594" t="inlineStr"/>
       <c r="E594" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F594" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="595">
@@ -14234,22 +14238,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F595" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -14260,18 +14264,18 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F596" t="n">
@@ -14286,18 +14290,18 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F597" t="n">
@@ -14312,22 +14316,22 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -14338,18 +14342,22 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
-      <c r="D599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F599" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -14360,22 +14368,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14386,22 +14394,18 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
-      <c r="D601" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D601" t="inlineStr"/>
       <c r="E601" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14412,22 +14416,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603">
@@ -14438,18 +14442,18 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -14464,18 +14468,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -14490,22 +14494,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -14516,42 +14520,38 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
-      <c r="D606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F606" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2025-02-21 20:30:00+05:30</t>
+          <t>2025-02-21 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C607" t="inlineStr"/>
-      <c r="D607" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
-      <c r="E607" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D607" t="inlineStr"/>
+      <c r="E607" t="inlineStr"/>
       <c r="F607" t="n">
         <v>2</v>
       </c>
@@ -14577,19 +14577,19 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2025-02-21 22:00:00+05:30</t>
+          <t>2025-02-21 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
       <c r="F609" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14649,19 +14649,19 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2025-02-21 23:30:00+05:30</t>
+          <t>2025-02-24 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Chicago Fed National Activity IndexJAN</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="614">
@@ -14685,12 +14685,12 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2025-02-24 19:00:00+05:30</t>
+          <t>2025-02-24 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Chicago Fed National Activity IndexJAN</t>
+          <t>Dallas Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
@@ -14721,19 +14721,19 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2025-02-24 21:00:00+05:30</t>
+          <t>2025-02-24 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Dallas Fed Manufacturing IndexFEB</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
       <c r="F617" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="618">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C620" t="inlineStr"/>
@@ -14793,12 +14793,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2025-02-24 22:00:00+05:30</t>
+          <t>2025-02-24 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
@@ -14829,12 +14829,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2025-02-24 23:30:00+05:30</t>
+          <t>2025-02-25 19:25:00+05:30</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>Redbook YoYFEB/22</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
@@ -14865,12 +14865,12 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2025-02-25 19:25:00+05:30</t>
+          <t>2025-02-25 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Redbook YoYFEB/22</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -14906,14 +14906,18 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr"/>
-      <c r="E627" t="inlineStr"/>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -14924,7 +14928,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -14942,7 +14946,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -14978,18 +14982,14 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr"/>
-      <c r="E631" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E631" t="inlineStr"/>
       <c r="F631" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="632">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15018,14 +15018,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr"/>
-      <c r="E633" t="inlineStr"/>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F633" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="634">
@@ -15036,29 +15040,25 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E634" t="inlineStr"/>
       <c r="F634" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2025-02-25 19:30:00+05:30</t>
+          <t>2025-02-25 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15094,14 +15094,14 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
       <c r="D637" t="inlineStr"/>
       <c r="E637" t="inlineStr"/>
       <c r="F637" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="638">
@@ -15112,14 +15112,14 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
       <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr"/>
       <c r="F638" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="639">
@@ -15130,14 +15130,14 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15166,14 +15166,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
       <c r="F641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -15197,12 +15197,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2025-02-25 20:30:00+05:30</t>
+          <t>2025-02-25 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15269,12 +15269,12 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2025-02-25 21:00:00+05:30</t>
+          <t>2025-02-25 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -15341,19 +15341,19 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2025-02-25 23:30:00+05:30</t>
+          <t>2025-02-26 03:00:00+05:30</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
       <c r="D651" t="inlineStr"/>
       <c r="E651" t="inlineStr"/>
       <c r="F651" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="652">
@@ -15374,24 +15374,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>2025-02-26 03:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>API Crude Oil Stock ChangeFEB/21</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
-      <c r="E653" t="inlineStr"/>
-      <c r="F653" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
@@ -746,12 +746,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -768,22 +768,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -794,12 +790,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -816,22 +812,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -842,15 +834,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.099M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -864,12 +860,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -886,18 +882,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,19 +908,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>3</v>
@@ -934,18 +930,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1088,26 +1088,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1114,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,26 +1144,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1178,22 +1174,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1364,22 +1364,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalDEC</t>
+          <t>S&amp;P Global Composite PMI FinalDEC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalDEC</t>
+          <t>S&amp;P Global Services PMI FinalDEC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1712,18 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1738,26 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,22 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1824,22 +1828,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2124,26 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2154,22 +2154,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2180,26 +2172,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2210,14 +2202,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2228,22 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2332,19 +2332,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>3</v>
@@ -2358,18 +2354,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2402,22 +2402,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2428,12 +2424,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2450,12 +2446,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -2472,22 +2468,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,15 +2490,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2520,18 +2516,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2946,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2972,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3174,26 +3174,22 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3204,22 +3200,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3230,18 +3230,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3256,18 +3256,18 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3282,18 +3282,18 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3308,14 +3308,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3330,12 +3326,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,26 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3584,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3644,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3682,14 +3682,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3704,26 +3700,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3734,18 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4036,26 +4036,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4066,22 +4066,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4092,26 +4096,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4152,26 +4156,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -4182,26 +4186,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4212,26 +4212,26 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,17 +4322,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4348,15 +4348,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4370,17 +4374,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4396,12 +4400,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4418,12 +4422,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4440,19 +4444,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4582,18 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -4608,22 +4612,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4634,26 +4642,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4664,18 +4672,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4686,18 +4702,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4708,18 +4732,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
@@ -4730,16 +4762,24 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4752,18 +4792,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -4774,26 +4822,22 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4804,24 +4848,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4834,26 +4870,18 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -4864,26 +4892,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4894,26 +4914,18 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4936,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,26 +4966,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4984,18 +4992,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -5010,24 +5018,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
         <v>3</v>
       </c>
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5784,18 +5784,18 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -5828,18 +5828,18 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -5968,26 +5968,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -6028,22 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -6176,22 +6176,18 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235">
@@ -6202,12 +6198,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6224,12 +6220,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6242,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,19 +6264,15 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
         <v>3</v>
@@ -6294,12 +6286,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,18 +6308,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -6338,12 +6334,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6356,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,18 +6378,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244">
@@ -6404,22 +6404,22 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6474,22 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6504,22 +6504,18 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6534,18 +6530,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6810,22 +6810,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Building Permits FinalDEC</t>
+          <t>Building Permits MoM FinalDEC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>1.482M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1.6M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -6840,22 +6840,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalDEC</t>
+          <t>Building Permits FinalDEC</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.482M</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.483M</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.6M</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7066,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -7096,22 +7096,26 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -7122,26 +7126,22 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -7620,18 +7620,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,19 +7860,15 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.044M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
         <v>3</v>
@@ -7886,17 +7882,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
@@ -7912,22 +7908,18 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -7938,15 +7930,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
         <v>3</v>
@@ -7960,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7982,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,18 +8000,22 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307">
@@ -8096,22 +8096,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -8122,22 +8126,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8148,26 +8156,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8178,22 +8186,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8208,12 +8212,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -8234,18 +8238,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8260,26 +8268,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -8290,26 +8298,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -8320,26 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8542,26 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -8572,26 +8568,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8602,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8632,22 +8628,18 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -8662,14 +8654,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr"/>
-      <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr"/>
+          <t>Core PCE Price Index MoMDEC</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8680,26 +8684,14 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -8710,26 +8702,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8740,18 +8732,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -8766,15 +8762,19 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>0.7%</t>
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337">
@@ -8930,26 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8960,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8990,22 +8986,22 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9016,26 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -9046,18 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,18 +9232,18 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.197M</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
@@ -9258,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9288,26 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>8M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9616,22 +9616,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9646,22 +9642,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9672,14 +9660,26 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+          <t>Balance of TradeDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ -93.0B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>ExportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
+          <t>$266.5B</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ 262B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,22 +9928,18 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -9954,22 +9950,18 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
@@ -9980,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10002,15 +9994,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
         <v>3</v>
@@ -10024,18 +10020,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10046,19 +10046,15 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.373M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
         <v>3</v>
@@ -10072,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10094,18 +10090,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.027M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10468,22 +10468,22 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>CPIJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>317.42</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>317.3</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -10494,22 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate YoYJAN</t>
+          <t>CPI s.aJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>2.9%</t>
-        </is>
-      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>318.2</t>
         </is>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -10520,7 +10516,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
@@ -10531,7 +10527,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F410" t="n">
@@ -10546,18 +10542,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -10572,22 +10568,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>CPIJAN</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.42</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>317.3</t>
         </is>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -10598,18 +10594,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>CPI s.aJAN</t>
+          <t>Core Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>318.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -10880,18 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10906,22 +10902,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -10932,22 +10928,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10958,14 +10950,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10980,18 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -11002,14 +10998,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11024,22 +11020,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11042,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -11072,18 +11068,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -11094,18 +11094,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,22 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11290,18 +11290,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11312,18 +11312,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
@@ -11334,18 +11338,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11356,14 +11364,14 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F450" t="n">
@@ -11378,22 +11386,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -11404,18 +11408,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11430,22 +11430,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -11456,14 +11456,14 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F454" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11870,8 +11870,16 @@
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
-      <c r="E473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="F473" t="n">
         <v>2</v>
       </c>
@@ -11964,7 +11972,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -11982,7 +11990,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -12108,14 +12116,14 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487">
@@ -12126,14 +12134,14 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -12144,14 +12152,18 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -12180,18 +12192,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12350,14 +12358,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12368,14 +12376,14 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr"/>
       <c r="F500" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
@@ -12386,7 +12394,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -12404,7 +12412,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
@@ -12422,7 +12430,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
@@ -12466,22 +12474,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12492,14 +12496,22 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
-      <c r="E506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>1.35M</t>
+        </is>
+      </c>
       <c r="F506" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507">
@@ -12536,18 +12548,22 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -12602,22 +12618,18 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512">
@@ -13092,22 +13104,14 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E536" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -13118,7 +13122,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13136,12 +13140,16 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13154,12 +13162,16 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13172,16 +13184,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E540" t="inlineStr"/>
       <c r="F540" t="n">
         <v>3</v>
       </c>
@@ -13194,16 +13202,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
         <v>3</v>
       </c>
@@ -13216,18 +13220,18 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F542" t="n">
@@ -13242,14 +13246,22 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr"/>
-      <c r="E543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -13384,7 +13396,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -13402,7 +13414,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
@@ -13474,7 +13486,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13492,14 +13504,14 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -13510,7 +13522,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -13528,14 +13540,14 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="559">
@@ -13546,7 +13558,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13564,7 +13576,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13582,14 +13594,14 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="562">
@@ -13618,7 +13630,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13636,14 +13648,14 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr"/>
       <c r="F564" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="565">
@@ -13762,14 +13774,14 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572">
@@ -13798,14 +13810,14 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr"/>
       <c r="E573" t="inlineStr"/>
       <c r="F573" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -14120,15 +14132,11 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14146,11 +14154,15 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14316,22 +14328,22 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14368,22 +14380,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -14394,18 +14406,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
-      <c r="D601" t="inlineStr"/>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14416,22 +14432,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14442,22 +14458,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -14468,22 +14484,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14494,18 +14506,18 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F605" t="n">
@@ -14888,7 +14900,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -14928,7 +14940,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15040,7 +15052,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15130,14 +15142,14 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -15166,14 +15178,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
       <c r="F641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -15202,7 +15214,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15256,7 +15268,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F652"/>
+  <dimension ref="A1:F657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,15 +746,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.099M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>3</v>
@@ -768,18 +772,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -790,12 +798,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -812,12 +820,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -834,18 +842,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -856,12 +868,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -878,22 +890,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -904,22 +912,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -930,19 +934,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
         <v>3</v>
@@ -1088,26 +1088,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1118,22 +1118,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1144,26 +1148,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1174,26 +1178,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1364,22 +1364,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalDEC</t>
+          <t>S&amp;P Global Services PMI FinalDEC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalDEC</t>
+          <t>S&amp;P Global Composite PMI FinalDEC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1712,22 +1712,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1738,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,26 +1798,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,18 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2124,26 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2154,14 +2154,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -2172,26 +2180,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2202,22 +2210,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2228,22 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2332,15 +2332,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>3</v>
@@ -2354,22 +2358,18 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -2424,18 +2424,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,22 +2450,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2472,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,19 +2498,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.045M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3</v>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,22 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,22 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3084,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3174,18 +3174,18 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations PrelJAN</t>
+          <t>Michigan Current Conditions PrelJAN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3200,18 +3200,18 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations PrelJAN</t>
+          <t>Michigan Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3226,18 +3226,18 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
+          <t>Michigan Consumer Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3252,26 +3252,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment PrelJAN</t>
+          <t>Michigan 5 Year Inflation Expectations PrelJAN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>73.2</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3282,22 +3278,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions PrelJAN</t>
+          <t>Michigan Consumer Sentiment PrelJAN</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>77.9</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3308,10 +3308,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - CornDEC</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12.074B</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
@@ -3326,12 +3330,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>3.1B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>12.074B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>3.1B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,18 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3640,26 +3648,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3670,26 +3678,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3700,12 +3704,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3719,7 +3723,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3730,7 +3734,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3738,14 +3742,10 @@
           <t>3.3%</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4036,26 +4036,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4066,26 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4096,26 +4092,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>315.61</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4156,26 +4152,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4186,22 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4212,26 +4212,26 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Production ChangeJAN/10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.765M</t>
+          <t>0.397M</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -4300,12 +4300,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/10</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>-1.304M</t>
+          <t>0.646M</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -4322,17 +4322,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>5.852M</t>
+          <t>-1.961M</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2.60M</t>
+          <t>-1.6M</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4348,19 +4348,15 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/10</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>3.077M</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1.1M</t>
-        </is>
-      </c>
+          <t>-0.255M</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="n">
         <v>3</v>
@@ -4374,17 +4370,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/10</t>
+          <t>EIA Gasoline Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>-1.961M</t>
+          <t>5.852M</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-1.6M</t>
+          <t>2.60M</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4400,12 +4396,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/10</t>
+          <t>EIA Crude Oil Imports ChangeJAN/10</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.646M</t>
+          <t>-1.304M</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
@@ -4422,12 +4418,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/10</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.397M</t>
+          <t>0.765M</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -4444,15 +4440,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/10</t>
+          <t>EIA Distillate Stocks ChangeJAN/10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>-0.255M</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>3.077M</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1.1M</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="n">
         <v>3</v>
@@ -4582,26 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,26 +4608,22 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4642,26 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4672,26 +4664,18 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>209.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4702,26 +4686,18 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4732,26 +4708,18 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -4762,24 +4730,16 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4792,18 +4752,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -4818,24 +4782,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4848,16 +4804,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4870,18 +4834,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -4892,18 +4864,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -4914,18 +4894,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>209.0K</t>
+        </is>
+      </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4936,26 +4924,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4966,22 +4954,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,18 +4984,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>46.3</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -5014,18 +5014,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>212.75K</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -5762,18 +5762,18 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5806,18 +5806,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5968,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -6024,26 +6028,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,12 +6202,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -6220,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6242,19 +6246,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="n">
         <v>3</v>
@@ -6268,18 +6268,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239">
@@ -6290,22 +6294,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240">
@@ -6316,12 +6320,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,12 +6342,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6360,12 +6364,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -6382,22 +6386,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6474,22 +6474,18 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6534,18 +6530,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/24</t>
+          <t>Baker Hughes Oil Rig CountJAN/24</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -6788,12 +6788,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/24</t>
+          <t>Baker Hughes Total Rigs CountJAN/24</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>576</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7204,22 +7204,26 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
@@ -7230,22 +7234,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7260,18 +7260,18 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>433.4</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -7286,18 +7286,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -7312,26 +7312,26 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
@@ -7816,22 +7816,18 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7842,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -7886,19 +7886,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7912,15 +7908,19 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="n">
         <v>3</v>
@@ -7934,12 +7934,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7956,12 +7956,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -7978,17 +7978,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,26 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8126,22 +8122,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -8152,26 +8152,22 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8182,18 +8178,22 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -8208,26 +8208,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8238,22 +8238,18 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -8268,22 +8264,26 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>1.1%</t>
-        </is>
-      </c>
       <c r="F316" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -8320,26 +8320,26 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8542,26 +8542,26 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
@@ -8572,18 +8572,22 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -8598,18 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8624,26 +8632,14 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8654,26 +8650,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8684,14 +8680,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr"/>
-      <c r="D332" t="inlineStr"/>
-      <c r="E332" t="inlineStr"/>
+          <t>Personal Spending MoMDEC</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8702,26 +8710,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8732,26 +8740,22 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8762,22 +8766,18 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
           <t>0.3%</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -8930,22 +8930,18 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8960,26 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -9016,26 +9012,26 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -9046,18 +9042,22 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9498,18 +9498,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Purchase IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>156.7</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>156.7</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9564,18 +9564,18 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
@@ -9794,22 +9794,26 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F377" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
@@ -9820,18 +9824,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9846,18 +9850,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F379" t="n">
@@ -9872,26 +9876,22 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -9902,18 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -10378,14 +10378,14 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr"/>
       <c r="F403" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10432,14 +10432,14 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
       <c r="F406" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="407">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,14 +10620,14 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,14 +10674,14 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422">
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
@@ -10880,18 +10880,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429">
@@ -10902,18 +10906,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -10924,18 +10932,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10950,14 +10958,14 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10972,22 +10980,18 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -10998,14 +11002,14 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F433" t="n">
@@ -11020,18 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -11042,22 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11068,18 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11094,22 +11098,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F437" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,14 +11264,14 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -11286,18 +11286,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11308,18 +11312,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -11334,22 +11334,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -11360,22 +11356,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -11386,18 +11382,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -11408,14 +11408,14 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F452" t="n">
@@ -11430,18 +11430,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -11452,22 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -12116,14 +12116,14 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="487">
@@ -12134,14 +12134,14 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -12412,14 +12412,14 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -12430,14 +12430,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12552,14 +12552,14 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F508" t="n">
@@ -12618,14 +12618,14 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F511" t="n">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -13086,14 +13086,22 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F535" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="536">
@@ -13130,22 +13138,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13156,16 +13156,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E538" t="inlineStr"/>
       <c r="F538" t="n">
         <v>3</v>
       </c>
@@ -13178,16 +13174,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13200,12 +13192,16 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F540" t="n">
         <v>3</v>
       </c>
@@ -13218,12 +13214,16 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr"/>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F541" t="n">
         <v>3</v>
       </c>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -13504,7 +13504,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13648,14 +13648,14 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
       <c r="D564" t="inlineStr"/>
       <c r="E564" t="inlineStr"/>
       <c r="F564" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="565">
@@ -13666,14 +13666,14 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr"/>
       <c r="F565" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="566">
@@ -13684,14 +13684,14 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="567">
@@ -13774,14 +13774,14 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr"/>
       <c r="E571" t="inlineStr"/>
       <c r="F571" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572">
@@ -14062,18 +14062,14 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14110,14 +14106,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14180,11 +14176,15 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14228,14 +14228,18 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -14250,22 +14254,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F595" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="596">
@@ -14276,18 +14280,18 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F596" t="n">
@@ -14302,18 +14306,18 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F597" t="n">
@@ -14328,22 +14332,18 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>68.7</t>
-        </is>
-      </c>
+      <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14354,18 +14354,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -14380,22 +14380,22 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F600" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -14406,22 +14406,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14432,18 +14432,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -14458,22 +14458,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="606">
@@ -14532,18 +14532,18 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F606" t="n">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15142,14 +15142,14 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15178,14 +15178,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
       <c r="F641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15386,6 +15386,96 @@
         <v>2</v>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2025-02-26 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>MBA Mortgage Market IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr"/>
+      <c r="D653" t="inlineStr"/>
+      <c r="E653" t="inlineStr"/>
+      <c r="F653" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2025-02-26 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr"/>
+      <c r="D654" t="inlineStr"/>
+      <c r="E654" t="inlineStr"/>
+      <c r="F654" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2025-02-26 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr"/>
+      <c r="D655" t="inlineStr"/>
+      <c r="E655" t="inlineStr"/>
+      <c r="F655" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2025-02-26 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr"/>
+      <c r="D656" t="inlineStr"/>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2025-02-26 17:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>MBA Purchase IndexFEB/21</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr"/>
+      <c r="D657" t="inlineStr"/>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F666"/>
+  <dimension ref="A1:F668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,18 +746,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
+          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.416M</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>-1.178M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-2.75M</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -768,22 +772,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeDEC/27</t>
+          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.717M</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.7M</t>
-        </is>
-      </c>
+          <t>0.041M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -794,12 +794,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeDEC/27</t>
+          <t>EIA Gasoline Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.323M</t>
+          <t>-0.959M</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -816,15 +816,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
+          <t>EIA Distillate Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.099M</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>6.406M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.1M</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3</v>
@@ -838,19 +842,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeDEC/27</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.406M</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-0.1M</t>
-        </is>
-      </c>
+          <t>-0.142M</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3</v>
@@ -864,12 +864,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeDEC/27</t>
+          <t>EIA Crude Oil Imports ChangeDEC/27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.959M</t>
+          <t>0.323M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -886,18 +886,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeDEC/27</t>
+          <t>EIA Gasoline Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.041M</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>7.717M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.7M</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -908,12 +912,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Heating Oil Stocks ChangeDEC/27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.142M</t>
+          <t>-0.416M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -930,22 +934,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeDEC/27</t>
+          <t>EIA Distillate Fuel Production ChangeDEC/27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.178M</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-2.75M</t>
-        </is>
-      </c>
+          <t>0.099M</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1088,26 +1088,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentDEC</t>
+          <t>ISM Manufacturing PricesDEC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1118,26 +1118,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIDEC</t>
+          <t>ISM Manufacturing New OrdersDEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>48.4</t>
-        </is>
-      </c>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1148,22 +1144,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersDEC</t>
+          <t>ISM Manufacturing EmploymentDEC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1174,26 +1174,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesDEC</t>
+          <t>ISM Manufacturing PMIDEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1364,22 +1364,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FinalDEC</t>
+          <t>S&amp;P Global Composite PMI FinalDEC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1394,22 +1394,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FinalDEC</t>
+          <t>S&amp;P Global Services PMI FinalDEC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1712,18 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>58.2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1738,26 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
+          <t>3.065M</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,22 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1824,22 +1828,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2124,26 +2124,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/04</t>
+          <t>Continuing Jobless ClaimsDEC/28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>201K</t>
+          <t>1867K</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>218K</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>213K</t>
+          <t>1848K</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -2154,22 +2154,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/04</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>213K</t>
-        </is>
-      </c>
+          <t>Fed Waller Speech</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>224K</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2180,26 +2172,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Total Vehicle SalesDEC</t>
+          <t>Initial Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16.8M</t>
+          <t>201K</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.5M</t>
+          <t>218K</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.3M</t>
+          <t>213K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2210,14 +2202,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fed Waller Speech</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Jobless Claims 4-week AverageJAN/04</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>213K</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>224K</t>
+        </is>
+      </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2228,22 +2228,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsDEC/28</t>
+          <t>Total Vehicle SalesDEC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1867K</t>
+          <t>16.8M</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>16.5M</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1848K</t>
+          <t>16.3M</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2332,18 +2332,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2354,12 +2358,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,19 +2380,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3</v>
@@ -2402,22 +2402,18 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2428,12 +2424,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.167M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2450,15 +2446,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-2.502M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,18 +2472,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2494,22 +2498,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.081M</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.278M</t>
+          <t>-0.632M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2916,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>256K</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>160K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2946,26 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2976,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3006,22 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,26 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3092,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3118,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>256K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>160K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3148,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/10</t>
+          <t>Baker Hughes Oil Rig CountJAN/10</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>480</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/10</t>
+          <t>Baker Hughes Total Rigs CountJAN/10</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -3558,26 +3558,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3588,18 +3588,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3614,26 +3618,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3644,18 +3644,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3670,22 +3674,18 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3700,26 +3700,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3730,26 +3730,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,18 +3970,18 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NOPA Crush Report</t>
+          <t>Fed Golsbee Speech</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -4546,14 +4546,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Fed Golsbee Speech</t>
+          <t>NOPA Crush Report</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -4582,17 +4582,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4612,22 +4612,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -4638,22 +4642,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4664,26 +4672,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4694,18 +4702,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4716,16 +4732,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4738,12 +4762,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4760,16 +4784,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4782,24 +4814,16 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4812,12 +4836,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4834,24 +4858,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4864,26 +4880,18 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4894,26 +4902,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4924,26 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4954,26 +4958,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -5040,22 +5040,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Business Inventories MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -5070,17 +5070,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>Business Inventories MoMNOV</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -5100,26 +5100,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -5266,22 +5266,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -5292,26 +5296,22 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -5322,22 +5322,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.483M</t>
+          <t>1.499M</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1.46M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/17</t>
+          <t>Baker Hughes Total Rigs CountJAN/17</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>580</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/17</t>
+          <t>Baker Hughes Oil Rig CountJAN/17</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>478</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -5564,18 +5564,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>$159.9B</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -5586,22 +5590,18 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
           <t>$159.9B</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$159.9B</t>
+          <t>$-15.8B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -5740,18 +5740,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5806,18 +5806,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5968,22 +5968,18 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -5998,22 +5994,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -6024,26 +6024,26 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -6080,18 +6080,18 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexJAN</t>
+          <t>Kansas Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -6106,18 +6106,18 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexJAN</t>
+          <t>Kansas Fed Composite IndexJAN</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -6176,19 +6176,15 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-3.07M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>0.6M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
         <v>3</v>
@@ -6202,15 +6198,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
         <v>3</v>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6474,22 +6474,22 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashJAN</t>
+          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -6504,22 +6504,18 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashJAN</t>
+          <t>S&amp;P Global Composite PMI FlashJAN</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -6534,18 +6530,22 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashJAN</t>
+          <t>S&amp;P Global Services PMI FlashJAN</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -6590,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6676,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6706,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7342,22 +7342,26 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -7368,18 +7372,22 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7394,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,22 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -7642,18 +7642,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7838,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,18 +7860,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7886,19 +7886,15 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.532M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7912,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7934,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7956,17 +7952,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -7982,12 +7978,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8004,15 +8000,19 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.028M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>3</v>
@@ -8096,26 +8096,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
@@ -8126,18 +8122,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>212.5K</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -8152,26 +8148,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>1858K</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1890K</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
@@ -8182,26 +8178,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,18 +8208,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8238,26 +8234,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8268,18 +8264,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,22 +8294,26 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -8320,26 +8324,22 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -8542,12 +8542,24 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F327" t="n">
         <v>2</v>
       </c>
@@ -8560,26 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -8590,18 +8602,22 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -8616,26 +8632,22 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -8646,26 +8658,26 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -8676,22 +8688,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8702,22 +8718,18 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8732,26 +8744,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8762,26 +8774,14 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
       <c r="F335" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -8852,15 +8852,19 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/31</t>
+          <t>Baker Hughes Oil Rig CountJAN/31</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr"/>
       <c r="F338" t="n">
         <v>3</v>
@@ -8874,19 +8878,15 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/31</t>
+          <t>Baker Hughes Total Rigs CountJAN/31</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="n">
         <v>3</v>
@@ -9476,18 +9476,18 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/31</t>
+          <t>MBA Mortgage Market IndexJAN/31</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>224.8</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="365">
@@ -9498,18 +9498,18 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/31</t>
+          <t>MBA 30-Year Mortgage RateJAN/31</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>6.97%</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/31</t>
+          <t>MBA Mortgage Refinance IndexJAN/31</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>224.8</t>
+          <t>584.3</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9542,12 +9542,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/31</t>
+          <t>MBA Mortgage ApplicationsJAN/31</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>584.3</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -9794,18 +9794,18 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ISM Services PricesJAN</t>
+          <t>ISM Services New OrdersJAN</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="F377" t="n">
@@ -9820,18 +9820,18 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentJAN</t>
+          <t>ISM Services Business ActivityJAN</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="F378" t="n">
@@ -9846,22 +9846,26 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityJAN</t>
+          <t>ISM Services PMIJAN</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>54.5</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>54.3</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -9872,26 +9876,22 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ISM Services PMIJAN</t>
+          <t>ISM Services PricesJAN</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>52.8</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -9902,18 +9902,18 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersJAN</t>
+          <t>ISM Services EmploymentJAN</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F381" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,22 +9972,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -9998,18 +9994,22 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -10020,19 +10020,15 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>3</v>
@@ -10046,22 +10042,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>-5.471M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>-1.5M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10072,18 +10068,22 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.186M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
+          <t>2.233M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>1.2M</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="389">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -10468,18 +10468,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYJAN</t>
+          <t>Inflation Rate MoMJAN</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -10494,18 +10494,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMJAN</t>
+          <t>Core Inflation Rate YoYJAN</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F409" t="n">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,14 +10746,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,22 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -10928,22 +10924,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10954,14 +10946,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
@@ -10976,22 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -11002,7 +10998,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
@@ -11013,11 +11009,11 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -11028,18 +11024,14 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>3.2%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11054,18 +11046,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11076,14 +11072,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11094,18 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11264,14 +11264,14 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F446" t="n">
@@ -11286,18 +11286,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -11308,18 +11312,14 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F448" t="n">
@@ -11334,22 +11334,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -11360,22 +11360,18 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
+      <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -11386,14 +11382,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11408,22 +11408,18 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -11434,14 +11430,14 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11456,18 +11452,22 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/14</t>
+          <t>Baker Hughes Oil Rig CountFEB/14</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/14</t>
+          <t>Baker Hughes Total Rigs CountFEB/14</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -12080,14 +12080,14 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="485">
@@ -12098,14 +12098,14 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="486">
@@ -12152,14 +12152,18 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -12188,18 +12192,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -12286,14 +12286,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -12340,14 +12340,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
@@ -12430,14 +12430,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="504">
@@ -12448,18 +12448,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12474,22 +12474,18 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="506">
@@ -12522,18 +12518,22 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F507" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -12544,14 +12544,14 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F508" t="n">
@@ -12566,22 +12566,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -12592,18 +12588,18 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F510" t="n">
@@ -12618,18 +12614,22 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -12900,14 +12900,22 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr"/>
-      <c r="E526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F526" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -12944,14 +12952,22 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr"/>
-      <c r="E528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F528" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="529">
@@ -12962,16 +12978,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E529" t="inlineStr"/>
       <c r="F529" t="n">
         <v>3</v>
       </c>
@@ -12984,16 +12996,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
-      <c r="E530" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E530" t="inlineStr"/>
       <c r="F530" t="n">
         <v>3</v>
       </c>
@@ -13006,22 +13014,14 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E531" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D531" t="inlineStr"/>
+      <c r="E531" t="inlineStr"/>
       <c r="F531" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13076,12 +13076,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F534" t="n">
         <v>3</v>
       </c>
@@ -13094,22 +13098,14 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D535" t="inlineStr"/>
+      <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -13138,7 +13134,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -13156,7 +13152,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13174,7 +13170,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13192,12 +13188,16 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F540" t="n">
         <v>3</v>
       </c>
@@ -13210,14 +13210,14 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>1879.0K</t>
         </is>
       </c>
       <c r="F541" t="n">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13504,14 +13504,14 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="557">
@@ -13522,14 +13522,14 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13576,14 +13576,14 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr"/>
       <c r="F560" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="561">
@@ -13594,14 +13594,14 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="562">
@@ -13612,14 +13612,14 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr"/>
       <c r="F562" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="563">
@@ -13630,14 +13630,14 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="564">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14088,14 +14088,14 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -14110,14 +14110,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14406,22 +14406,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -14432,18 +14432,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>4.17M</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603">
@@ -14454,22 +14458,18 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>4.17M</t>
-        </is>
-      </c>
+      <c r="D603" t="inlineStr"/>
       <c r="E603" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="604">
@@ -14480,22 +14480,22 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F604" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="605">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -15142,7 +15142,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15178,14 +15178,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
       <c r="F641" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="642">
@@ -15196,14 +15196,14 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr"/>
       <c r="F642" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="643">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,14 +15502,14 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr"/>
       <c r="F659" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="660">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -15556,14 +15556,14 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr"/>
       <c r="F662" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="663">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -15605,37 +15605,73 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2025-02-26 17:30:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr"/>
       <c r="E665" t="inlineStr"/>
       <c r="F665" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2025-02-26 17:30:00+05:30</t>
+          <t>2025-02-26 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
       <c r="D666" t="inlineStr"/>
       <c r="E666" t="inlineStr"/>
       <c r="F666" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2025-02-26 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>New Home SalesJAN</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr"/>
+      <c r="D667" t="inlineStr"/>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2025-02-26 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr"/>
+      <c r="D668" t="inlineStr"/>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F668"/>
+  <dimension ref="A1:F681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,26 +1712,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1742,18 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1768,19 +1772,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1798,26 +1798,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1828,18 +1828,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1854,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,22 +1884,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,22 +2332,18 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2380,18 +2376,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2402,15 +2402,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2424,18 +2428,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2446,19 +2454,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2472,22 +2476,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,12 +2520,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -2886,26 +2886,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2912,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2942,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2972,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3002,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,26 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3148,22 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,22 +3558,18 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3588,12 +3584,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3603,11 +3599,11 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3618,18 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -3644,26 +3644,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3674,18 +3674,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -3700,26 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
@@ -3730,26 +3730,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,26 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4066,22 +4062,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4096,22 +4092,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4126,26 +4122,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4156,22 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4186,18 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,26 +4582,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,26 +4608,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4642,26 +4638,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>210K</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4672,26 +4664,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -4702,26 +4690,26 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4732,24 +4720,16 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1870K</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>1870.0K</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4762,12 +4742,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4784,24 +4764,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4814,18 +4786,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -4836,16 +4816,24 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4858,12 +4846,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -4880,16 +4868,24 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>3</v>
       </c>
@@ -4902,12 +4898,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4921,7 +4917,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,22 +4928,26 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4958,22 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4984,26 +4988,18 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -5014,22 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5040,26 +5040,26 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>NAHB Housing Market IndexJAN</t>
+          <t>Retail Inventories Ex Autos MoMNOV</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189">
@@ -5100,26 +5100,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoMNOV</t>
+          <t>NAHB Housing Market IndexJAN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -5266,26 +5266,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Building Permits PrelDEC</t>
+          <t>Building Permits MoM PrelDEC</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>1.483M</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1.46M</t>
-        </is>
-      </c>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1.48M</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5296,22 +5292,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Housing Starts MoMDEC</t>
+          <t>Housing StartsDEC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>1.499M</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.32M</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>1.32M</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -5322,26 +5322,22 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Housing StartsDEC</t>
+          <t>Housing Starts MoMDEC</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>1.499M</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>1.32M</t>
-        </is>
-      </c>
+          <t>15.8%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1.32M</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -5352,22 +5348,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelDEC</t>
+          <t>Building Permits PrelDEC</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>1.483M</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>1.46M</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>1.48M</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -5564,22 +5564,18 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsNOV</t>
+          <t>Foreign Bond InvestmentNOV</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>$79B</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>$159.9B</t>
-        </is>
-      </c>
+          <t>$-15.8B</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -5590,18 +5586,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsNOV</t>
+          <t>Net Long-term TIC FlowsNOV</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
+          <t>$79B</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
           <t>$159.9B</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentNOV</t>
+          <t>Overall Net Capital FlowsNOV</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>$-15.8B</t>
+          <t>$159.9B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -5740,18 +5740,18 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/17</t>
+          <t>MBA Mortgage Market IndexJAN/17</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>224.6</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/17</t>
+          <t>MBA Purchase IndexJAN/17</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -5784,12 +5784,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/17</t>
+          <t>MBA Mortgage Refinance IndexJAN/17</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>558.8</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -5806,18 +5806,18 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/17</t>
+          <t>MBA 30-Year Mortgage RateJAN/17</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>224.6</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/17</t>
+          <t>MBA Mortgage ApplicationsJAN/17</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>558.8</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -5968,22 +5968,26 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/18</t>
+          <t>Initial Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>213.5K</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>213.0K</t>
+          <t>219K</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227">
@@ -5994,26 +5998,26 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/18</t>
+          <t>Continuing Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>1899K</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>220K</t>
+          <t>1860K</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>219K</t>
+          <t>1861K</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228">
@@ -6024,22 +6028,18 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/11</t>
+          <t>Jobless Claims 4-week AverageJAN/18</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>1899K</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>1860K</t>
-        </is>
-      </c>
+          <t>213.5K</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1861K</t>
+          <t>213.0K</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,22 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>2.5M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6224,18 +6224,22 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -6246,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,12 +6338,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -6356,15 +6360,19 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>6.16%</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>-3.07M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>0.6M</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
         <v>3</v>
@@ -6378,22 +6386,18 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.068M</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
@@ -6404,22 +6408,18 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-0.473M</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -6590,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6620,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -6650,22 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,26 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6740,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
@@ -7066,26 +7066,26 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMDEC</t>
+          <t>Non Defense Goods Orders Ex AirDEC</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -7096,26 +7096,22 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMDEC</t>
+          <t>Durable Goods Orders ex Defense MoMDEC</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
       <c r="F270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -7126,22 +7122,26 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMDEC</t>
+          <t>Durable Goods Orders Ex Transp MoMDEC</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>-2.4%</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>0.4%</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -7152,26 +7152,26 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirDEC</t>
+          <t>Durable Goods Orders MoMDEC</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -7342,26 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -7372,22 +7368,18 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -7402,22 +7394,26 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -7428,18 +7424,22 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,18 +7620,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -7708,18 +7708,18 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
@@ -7730,18 +7730,22 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
+          <t>Wholesale Inventories MoM AdvDEC</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
           <t>0.2%</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -7756,22 +7760,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Goods Trade Balance AdvDEC</t>
+          <t>Retail Inventories Ex Autos MoM AdvDEC</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>$-122.11B</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>$-105.4B</t>
-        </is>
-      </c>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>$ -106B</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -7786,22 +7786,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Wholesale Inventories MoM AdvDEC</t>
+          <t>Goods Trade Balance AdvDEC</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>$-122.11B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$-105.4B</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>$ -106B</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,18 +7838,22 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -7860,22 +7864,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -7886,12 +7890,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7930,12 +7934,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7952,17 +7956,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>3.463M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>3.2M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -7978,12 +7982,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>-0.333M</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -8000,19 +8004,15 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="n">
         <v>3</v>
@@ -8096,18 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,22 +8122,26 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>207K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>220K</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312">
@@ -8148,26 +8152,26 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>1858K</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1890K</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313">
@@ -8178,26 +8182,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -8208,22 +8212,26 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
@@ -8234,26 +8242,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316">
@@ -8264,22 +8272,18 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8294,26 +8298,22 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
@@ -8324,18 +8324,18 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.250%</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>4.250%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,26 +8572,14 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
       <c r="F328" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,26 +8590,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8632,22 +8620,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8658,26 +8650,22 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -8688,26 +8676,22 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
@@ -8718,18 +8702,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -8744,26 +8732,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -8774,12 +8762,24 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr"/>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
+          <t>PCE Price Index YoYDEC</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
       <c r="F335" t="n">
         <v>2</v>
       </c>
@@ -8792,26 +8792,26 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>Personal Income MoMDEC</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
@@ -8930,18 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -8956,26 +8960,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8986,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -9012,22 +9016,18 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9042,26 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -9232,22 +9232,26 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -9258,22 +9262,26 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -9284,26 +9292,22 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -9314,26 +9318,22 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -9616,18 +9616,18 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$266.5B</t>
+          <t>$364.9B</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 262B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9642,26 +9642,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>$ -93.0B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -9672,14 +9660,22 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F372" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
@@ -9690,18 +9686,22 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.373M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,17 +9994,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -10020,15 +10020,19 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
         <v>3</v>
@@ -10042,22 +10046,22 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -10068,22 +10072,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.027M</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,12 +10116,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bowman Speech</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423">
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,14 +10928,14 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
@@ -10946,22 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432">
@@ -10972,7 +10976,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
@@ -10983,11 +10987,11 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,18 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,14 +11024,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
@@ -11046,22 +11050,18 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="436">
@@ -11072,18 +11072,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -11094,18 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11478,22 +11478,22 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -11504,14 +11504,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11526,14 +11530,18 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Manufacturing Production MoMJAN</t>
         </is>
       </c>
       <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F457" t="n">
@@ -11548,18 +11556,14 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11574,22 +11578,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
@@ -12152,18 +12152,14 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr"/>
       <c r="F488" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489">
@@ -12174,14 +12170,18 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -12268,14 +12268,14 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -12286,14 +12286,14 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr"/>
       <c r="F495" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -12340,14 +12340,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
@@ -12430,14 +12430,14 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -12448,22 +12448,18 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="505">
@@ -12518,22 +12514,18 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F507" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="508">
@@ -12544,18 +12536,22 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F508" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -12566,18 +12562,22 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
@@ -12614,18 +12614,18 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F511" t="n">
@@ -12900,22 +12900,14 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr"/>
       <c r="F526" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="527">
@@ -13050,22 +13042,18 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F533" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -13076,16 +13064,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
         <v>3</v>
       </c>
@@ -13098,12 +13082,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F535" t="n">
         <v>3</v>
       </c>
@@ -13116,7 +13104,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13134,14 +13122,22 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F537" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="538">
@@ -13152,7 +13148,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13170,12 +13166,16 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13210,16 +13210,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E541" t="inlineStr"/>
       <c r="F541" t="n">
         <v>3</v>
       </c>
@@ -13232,16 +13228,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
         <v>3</v>
       </c>
@@ -13254,14 +13246,22 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr"/>
-      <c r="E543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F543" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="544">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
@@ -13486,14 +13486,14 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr"/>
       <c r="F555" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -13540,7 +13540,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -13576,14 +13576,14 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr"/>
       <c r="F560" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="561">
@@ -13594,14 +13594,14 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562">
@@ -13612,14 +13612,14 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr"/>
       <c r="F562" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="563">
@@ -13630,14 +13630,14 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13684,14 +13684,14 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="567">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
@@ -13720,14 +13720,14 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr"/>
       <c r="E568" t="inlineStr"/>
       <c r="F568" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="569">
@@ -13738,14 +13738,14 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14062,18 +14062,14 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14088,14 +14084,14 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr"/>
       <c r="E588" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F588" t="n">
@@ -14110,14 +14106,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14154,14 +14150,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F591" t="n">
@@ -14228,18 +14228,22 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F594" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="595">
@@ -14250,18 +14254,14 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D595" t="inlineStr"/>
       <c r="E595" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F595" t="n">
@@ -14276,22 +14276,22 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -14302,18 +14302,18 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F597" t="n">
@@ -14328,18 +14328,18 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F598" t="n">
@@ -14354,18 +14354,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F599" t="n">
@@ -14380,18 +14380,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -14406,18 +14406,18 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F601" t="n">
@@ -14432,22 +14432,22 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F602" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -14458,14 +14458,18 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>67.8</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F603" t="n">
@@ -14480,18 +14484,14 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>67.8</t>
-        </is>
-      </c>
+      <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F604" t="n">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="606">
@@ -14532,18 +14532,18 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F606" t="n">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14756,7 +14756,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -14882,18 +14882,14 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr"/>
-      <c r="E625" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E625" t="inlineStr"/>
       <c r="F625" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="626">
@@ -14904,7 +14900,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -14922,14 +14918,18 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr"/>
-      <c r="E627" t="inlineStr"/>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F627" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="628">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -14976,7 +14976,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15030,18 +15030,14 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr"/>
-      <c r="E633" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E633" t="inlineStr"/>
       <c r="F633" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="634">
@@ -15052,14 +15048,18 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
-      <c r="E634" t="inlineStr"/>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F634" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635">
@@ -15142,14 +15142,14 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -15196,14 +15196,14 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
       <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr"/>
       <c r="F642" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="643">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15394,14 +15394,14 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="654">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,14 +15502,14 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr"/>
       <c r="E659" t="inlineStr"/>
       <c r="F659" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="660">
@@ -15520,14 +15520,14 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr"/>
       <c r="F660" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="661">
@@ -15538,14 +15538,14 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr"/>
       <c r="F661" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="662">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15674,6 +15674,240 @@
         <v>2</v>
       </c>
     </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2025-02-26 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr"/>
+      <c r="D669" t="inlineStr"/>
+      <c r="E669" t="inlineStr"/>
+      <c r="F669" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2025-02-26 20:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>New Home SalesJAN</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr"/>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr"/>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr"/>
+      <c r="D672" t="inlineStr"/>
+      <c r="E672" t="inlineStr"/>
+      <c r="F672" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr"/>
+      <c r="D673" t="inlineStr"/>
+      <c r="E673" t="inlineStr"/>
+      <c r="F673" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr"/>
+      <c r="D674" t="inlineStr"/>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr"/>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr"/>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" t="inlineStr"/>
+      <c r="F676" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr"/>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr"/>
+      <c r="D678" t="inlineStr"/>
+      <c r="E678" t="inlineStr"/>
+      <c r="F678" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr"/>
+      <c r="D679" t="inlineStr"/>
+      <c r="E679" t="inlineStr"/>
+      <c r="F679" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr"/>
+      <c r="D680" t="inlineStr"/>
+      <c r="E680" t="inlineStr"/>
+      <c r="F680" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr"/>
+      <c r="D681" t="inlineStr"/>
+      <c r="E681" t="inlineStr"/>
+      <c r="F681" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F681"/>
+  <dimension ref="A1:F694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -1772,18 +1772,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,19 +1798,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1828,18 +1824,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,26 +1854,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1884,26 +1884,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,22 +2376,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2402,19 +2398,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2428,22 +2420,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -2454,15 +2442,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2476,18 +2468,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2498,12 +2494,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2520,18 +2516,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2886,22 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -2912,26 +2916,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
@@ -2942,26 +2942,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -2972,26 +2968,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3002,26 +2998,26 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3032,26 +3028,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3062,22 +3058,26 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3088,22 +3088,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3114,26 +3118,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,10 +3330,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3348,14 +3352,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,18 +3558,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -3584,26 +3588,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3614,26 +3618,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3644,26 +3648,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3689,11 +3689,11 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3704,18 +3704,22 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -3730,22 +3734,18 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,18 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4062,26 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4122,22 +4122,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,26 +4152,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -4582,22 +4582,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -4608,26 +4612,18 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -4638,22 +4634,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>217K</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>210K</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -4664,22 +4664,26 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
@@ -4690,12 +4694,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4709,7 +4713,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -4720,16 +4724,24 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
+          <t>1859K</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1870K</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>1870.0K</t>
+        </is>
+      </c>
       <c r="F176" t="n">
         <v>3</v>
       </c>
@@ -4742,12 +4754,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -4764,16 +4776,24 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>11.9</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4786,26 +4806,18 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+          <t>31.90</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -4816,24 +4828,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
         <v>3</v>
       </c>
@@ -4846,16 +4850,20 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4868,26 +4876,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4898,26 +4906,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -4928,22 +4932,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4958,26 +4962,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -4988,16 +4992,20 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5010,26 +5018,18 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -5378,26 +5378,22 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -5408,22 +5404,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5464,22 +5460,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5494,22 +5490,26 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,12 +6176,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -6198,22 +6198,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2.332M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2.5M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
@@ -6224,22 +6224,18 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-1.017M</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.043M</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237">
@@ -6250,12 +6246,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6272,12 +6268,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateJAN/23</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>6.96%</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6294,12 +6290,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6316,12 +6312,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6338,18 +6334,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-0.043M</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>-1.017M</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -6360,22 +6360,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>2.332M</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>2.5M</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.068M</t>
+          <t>-1.125M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>30-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>6.96%</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -6560,26 +6560,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -6590,26 +6586,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
@@ -6620,26 +6616,26 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253">
@@ -6650,22 +6646,22 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -6680,26 +6676,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -6710,22 +6706,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -6740,18 +6736,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>71.1</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2-Year Note Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>4.211%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>4.140%</t>
+          <t>4.211%</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -7204,22 +7204,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>House Price Index MoMNOV</t>
+          <t>House Price IndexNOV</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>433.4</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>433</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -7234,18 +7230,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
+          <t>House Price Index YoYNOV</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -7260,22 +7256,26 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>House Price Index YoYNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
@@ -7286,26 +7286,26 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYNOV</t>
+          <t>House Price Index MoMNOV</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278">
@@ -7316,18 +7316,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>House Price IndexNOV</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMNOV</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>433.4</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2-Year FRN Auction</t>
+          <t>42-Day Bill Auction</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>0.098%</t>
+          <t>4.260%</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -7528,12 +7528,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>42-Day Bill Auction</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>4.260%</t>
+          <t>0.098%</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Money SupplyDEC</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>$21.53T</t>
+          <t>4.457%</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>7-Year Note Auction</t>
+          <t>Money SupplyDEC</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>4.457%</t>
+          <t>$21.53T</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.028M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,22 +7838,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -7864,22 +7860,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>-4.994M</t>
+          <t>2.957M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>1.5M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -7890,12 +7886,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.326M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -7912,12 +7908,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7934,12 +7930,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.532M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -7956,22 +7952,22 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>-4.994M</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -7982,18 +7978,22 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>-0.333M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr"/>
+          <t>3.463M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>3.2M</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8350,18 +8350,22 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Pending Home Sales YoYDEC</t>
+          <t>Pending Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>-5.0%</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>-5.5%</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -8376,22 +8380,18 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pending Home Sales MoMDEC</t>
+          <t>Pending Home Sales YoYDEC</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>-5.5%</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+          <t>-5.0%</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -8542,22 +8542,22 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,14 +8572,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr"/>
-      <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
@@ -8590,26 +8602,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -8620,26 +8632,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -8650,12 +8662,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -8676,22 +8688,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.8%</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -8702,26 +8718,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -8732,26 +8748,14 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
       <c r="F334" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335">
@@ -8762,22 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8792,26 +8796,22 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337">
@@ -8930,26 +8930,22 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342">
@@ -8960,22 +8956,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8986,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -9016,18 +9012,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -9042,26 +9042,26 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>-0.034M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.16M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,17 +9994,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2.233M</t>
+          <t>8.664M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>1.2M</t>
+          <t>2.6M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -10020,22 +10020,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>-5.471M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>-1.5M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
@@ -10046,22 +10046,18 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>8.664M</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>2.6M</t>
-        </is>
-      </c>
+          <t>-0.186M</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr"/>
       <c r="F387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -10072,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10094,12 +10090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.034M</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10116,15 +10112,19 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>3</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -10728,14 +10728,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10764,14 +10764,14 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Crude Oil Imports ChangeFEB/07</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423">
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,18 +10902,14 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10928,18 +10924,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
@@ -10950,22 +10950,18 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -10976,22 +10972,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="433">
@@ -11002,18 +10998,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11024,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F435" t="n">
@@ -11072,22 +11072,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11264,18 +11264,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -11286,22 +11290,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -11312,18 +11312,18 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -11334,22 +11334,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450">
@@ -11360,18 +11360,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-0.1%</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -11382,18 +11386,14 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -11408,18 +11408,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453">
@@ -11430,14 +11434,14 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F453" t="n">
@@ -11452,22 +11456,18 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F454" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
@@ -12098,14 +12098,14 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="486">
@@ -12116,14 +12116,14 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="487">
@@ -12170,18 +12170,14 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="490">
@@ -12192,14 +12188,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -12340,14 +12340,14 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="500">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F504" t="n">
@@ -12470,14 +12470,14 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F505" t="n">
@@ -12492,14 +12492,14 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F506" t="n">
@@ -12514,18 +12514,22 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>1.45M</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F507" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -12562,18 +12566,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr">
         <is>
-          <t>1.45M</t>
+          <t>1.39M</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F509" t="n">
@@ -12588,18 +12592,18 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
       <c r="D510" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F510" t="n">
@@ -12614,22 +12618,18 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512">
@@ -12900,14 +12900,22 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr"/>
-      <c r="E526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F526" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="527">
@@ -12918,18 +12926,18 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F527" t="n">
@@ -12944,22 +12952,18 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
+      <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
-          <t>220.0K</t>
+          <t>219.0K</t>
         </is>
       </c>
       <c r="F528" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -12970,7 +12974,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -12988,7 +12992,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -13006,7 +13010,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
@@ -13024,7 +13028,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -13064,12 +13068,16 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F534" t="n">
         <v>3</v>
       </c>
@@ -13082,16 +13090,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E535" t="inlineStr"/>
       <c r="F535" t="n">
         <v>3</v>
       </c>
@@ -13104,7 +13108,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -13148,7 +13152,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -13166,16 +13170,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="n">
         <v>3</v>
       </c>
@@ -13188,18 +13188,22 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>219.0K</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F540" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
@@ -13210,7 +13214,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -13228,12 +13232,16 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr"/>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F542" t="n">
         <v>3</v>
       </c>
@@ -13246,22 +13254,14 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="inlineStr"/>
       <c r="F543" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -13468,14 +13468,14 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr"/>
       <c r="F554" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555">
@@ -13486,14 +13486,14 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr"/>
       <c r="F555" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="556">
@@ -13504,14 +13504,14 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -13522,14 +13522,14 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="558">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -13558,14 +13558,14 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="560">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -13630,14 +13630,14 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr"/>
       <c r="E563" t="inlineStr"/>
       <c r="F563" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="564">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -13684,14 +13684,14 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="567">
@@ -13702,14 +13702,14 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr"/>
       <c r="E567" t="inlineStr"/>
       <c r="F567" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="568">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14062,14 +14062,18 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14128,14 +14132,14 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -14176,15 +14180,11 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14202,22 +14202,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F593" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="594">
@@ -14228,18 +14228,18 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -14254,18 +14254,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
-      <c r="D595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F595" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="596">
@@ -14276,22 +14280,22 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F596" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="597">
@@ -14302,22 +14306,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="598">
@@ -14328,22 +14332,18 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
-      <c r="D598" t="inlineStr">
-        <is>
-          <t>67.3</t>
-        </is>
-      </c>
+      <c r="D598" t="inlineStr"/>
       <c r="E598" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="599">
@@ -14354,22 +14354,22 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F599" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="600">
@@ -14380,18 +14380,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -14506,22 +14506,22 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F605" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -14532,22 +14532,22 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F606" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="607">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -14918,18 +14918,14 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr"/>
-      <c r="E627" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E627" t="inlineStr"/>
       <c r="F627" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="628">
@@ -14940,14 +14936,18 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr"/>
-      <c r="E628" t="inlineStr"/>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F628" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="629">
@@ -14958,14 +14958,18 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr"/>
-      <c r="E629" t="inlineStr"/>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F629" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="630">
@@ -14976,7 +14980,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
@@ -14994,7 +14998,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -15012,7 +15016,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15048,18 +15052,14 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
-      <c r="E634" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E634" t="inlineStr"/>
       <c r="F634" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="635">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
@@ -15142,14 +15142,14 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="640">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15178,14 +15178,14 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
       <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
       <c r="F641" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="642">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Dallas Fed Services Revenues IndexFEB</t>
+          <t>Dallas Fed Services IndexFEB</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Dallas Fed Services IndexFEB</t>
+          <t>Dallas Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -15394,14 +15394,14 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="654">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15430,14 +15430,14 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr"/>
       <c r="F655" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="656">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15520,14 +15520,14 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr"/>
       <c r="E660" t="inlineStr"/>
       <c r="F660" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="661">
@@ -15538,14 +15538,14 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr"/>
       <c r="F661" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="662">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -15736,14 +15736,14 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr"/>
       <c r="E672" t="inlineStr"/>
       <c r="F672" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="673">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -15862,14 +15862,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="680">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -15908,6 +15908,240 @@
         <v>3</v>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr"/>
+      <c r="D682" t="inlineStr"/>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr"/>
+      <c r="D683" t="inlineStr"/>
+      <c r="E683" t="inlineStr"/>
+      <c r="F683" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr"/>
+      <c r="D684" t="inlineStr"/>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr"/>
+      <c r="D685" t="inlineStr"/>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr"/>
+      <c r="D686" t="inlineStr"/>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr"/>
+      <c r="D687" t="inlineStr"/>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr"/>
+      <c r="D688" t="inlineStr"/>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr"/>
+      <c r="D689" t="inlineStr"/>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2025-02-26 21:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr"/>
+      <c r="D690" t="inlineStr"/>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2025-02-26 22:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>17-Week Bill Auction</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr"/>
+      <c r="D691" t="inlineStr"/>
+      <c r="E691" t="inlineStr"/>
+      <c r="F691" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2025-02-26 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Fed Bostic Speech</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr"/>
+      <c r="D692" t="inlineStr"/>
+      <c r="E692" t="inlineStr"/>
+      <c r="F692" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2025-02-26 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr"/>
+      <c r="D693" t="inlineStr"/>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2025-02-26 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr"/>
+      <c r="D694" t="inlineStr"/>
+      <c r="E694" t="inlineStr"/>
+      <c r="F694" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F694"/>
+  <dimension ref="A1:F700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,12 +956,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.265%</t>
+          <t>4.240%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -978,12 +978,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.240%</t>
+          <t>4.265%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountJAN/03</t>
+          <t>Baker Hughes Total Rigs CountJAN/03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountJAN/03</t>
+          <t>Baker Hughes Oil Rig CountJAN/03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>482</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.205%</t>
+          <t>4.110%</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.110%</t>
+          <t>4.205%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1712,26 +1712,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISM Services PMIDEC</t>
+          <t>ISM Services New OrdersDEC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>54.1</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1742,26 +1742,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISM Services PricesDEC</t>
+          <t>JOLTs Job OpeningsNOV</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>8.098M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>7.70M</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>7.69M</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1772,18 +1772,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsNOV</t>
+          <t>ISM Services EmploymentDEC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.065M</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3.31M</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -1798,18 +1802,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISM Services Business ActivityDEC</t>
+          <t>JOLTs Job QuitsNOV</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>3.065M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>3.31M</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -1824,22 +1828,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ISM Services EmploymentDEC</t>
+          <t>ISM Services PricesDEC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -1854,22 +1858,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsNOV</t>
+          <t>ISM Services PMIDEC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>8.098M</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7.70M</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.69M</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -1884,19 +1888,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ISM Services New OrdersDEC</t>
+          <t>ISM Services Business ActivityDEC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>54.1</t>
@@ -1984,18 +1984,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/03</t>
+          <t>MBA 30-Year Mortgage RateJAN/03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>401.1</t>
+          <t>6.99%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/03</t>
+          <t>MBA Mortgage Market IndexJAN/03</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>168.4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/03</t>
+          <t>MBA Mortgage ApplicationsJAN/03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>168.4</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2050,18 +2050,18 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/03</t>
+          <t>MBA Mortgage Refinance IndexJAN/03</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>401.1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/03</t>
+          <t>MBA Purchase IndexJAN/03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2332,18 +2332,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
+          <t>EIA Gasoline Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.045M</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>6.33M</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2354,12 +2358,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Gasoline Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-2.502M</t>
+          <t>-0.081M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -2376,18 +2380,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/03</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.278M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>-0.959M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>-0.6M</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2398,15 +2406,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
+          <t>EIA Distillate Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>-0.167M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>6.071M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3</v>
@@ -2420,12 +2432,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>-0.632M</t>
+          <t>0.045M</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -2442,19 +2454,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/03</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6.071M</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
+          <t>-0.167M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3</v>
@@ -2468,22 +2476,18 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/03</t>
+          <t>EIA Crude Oil Imports ChangeJAN/03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-0.959M</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>-0.6M</t>
-        </is>
-      </c>
+          <t>0.278M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -2494,12 +2498,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/03</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>-0.081M</t>
+          <t>-2.502M</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -2516,22 +2520,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/03</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>6.33M</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1.5M</t>
-        </is>
-      </c>
+          <t>-0.632M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -2886,26 +2886,26 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nonfarm Payrolls PrivateDEC</t>
+          <t>Non Farm PayrollsDEC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>223K</t>
+          <t>256K</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>135K</t>
+          <t>160K</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>185K</t>
+          <t>200K</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -2916,22 +2916,26 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>U-6 Unemployment Rate</t>
+          <t>Unemployment RateDEC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7.5%</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -2942,22 +2946,26 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Government PayrollsDEC</t>
+          <t>Average Hourly Earnings MoMDEC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>33K</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>15K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -2968,26 +2976,26 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Manufacturing PayrollsDEC</t>
+          <t>Average Hourly Earnings YoY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-13K</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>29K</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -2998,26 +3006,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Average Weekly HoursDEC</t>
+          <t>Participation RateDEC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3028,26 +3032,26 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings YoY</t>
+          <t>Manufacturing PayrollsDEC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>-13K</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>29K</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
@@ -3058,26 +3062,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Average Hourly Earnings MoMDEC</t>
+          <t>Government PayrollsDEC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>33K</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>15K</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3088,26 +3088,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Unemployment RateDEC</t>
+          <t>U-6 Unemployment Rate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4.1%</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3118,22 +3114,26 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Participation RateDEC</t>
+          <t>Nonfarm Payrolls PrivateDEC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>223K</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>135K</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>185K</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -3144,26 +3144,26 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Non Farm PayrollsDEC</t>
+          <t>Average Weekly HoursDEC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>256K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>160K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>200K</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - CornDEC</t>
+          <t>Quarterly Grain Stocks - WheatDEC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>12.074B</t>
+          <t>1.57B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -3330,14 +3330,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - SoyDEC</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.1B</t>
-        </is>
-      </c>
+          <t>WASDE Report</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
@@ -3352,10 +3348,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>WASDE Report</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Quarterly Grain Stocks - SoyDEC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.1B</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Quarterly Grain Stocks - WheatDEC</t>
+          <t>Quarterly Grain Stocks - CornDEC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.57B</t>
+          <t>12.074B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
+          <t>PPI MoMDEC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3588,22 +3588,18 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PPI YoYDEC</t>
+          <t>PPIDEC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
+          <t>146.842</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -3618,26 +3614,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Core PPI MoMDEC</t>
+          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
@@ -3648,18 +3640,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYDEC</t>
+          <t>Core PPI YoYDEC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.8%</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -3674,26 +3670,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PPI MoMDEC</t>
+          <t>PPI YoYDEC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3704,26 +3700,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Core PPI YoYDEC</t>
+          <t>Core PPI MoMDEC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3734,18 +3730,22 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PPIDEC</t>
+          <t>PPI Ex Food, Energy and Trade MoMDEC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>146.842</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/10</t>
+          <t>MBA Purchase IndexJAN/10</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -3948,18 +3948,18 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/10</t>
+          <t>MBA Mortgage Market IndexJAN/10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>224.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/10</t>
+          <t>MBA Mortgage ApplicationsJAN/10</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>575.6</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -3992,18 +3992,18 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/10</t>
+          <t>MBA 30-Year Mortgage RateJAN/10</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>224.4</t>
+          <t>7.09%</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/10</t>
+          <t>MBA Mortgage Refinance IndexJAN/10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>575.6</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -4036,22 +4036,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CPIDEC</t>
+          <t>NY Empire State Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>-12.60</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>315.61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>315.6</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4066,18 +4066,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CPI s.aDEC</t>
+          <t>CPIDEC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>317.685</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
+          <t>315.61</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>315.61</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>317.4</t>
+          <t>315.6</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4092,26 +4096,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Core Inflation Rate YoYDEC</t>
+          <t>CPI s.aDEC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>317.685</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>317.4</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4122,22 +4122,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Core Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate YoYDEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4152,22 +4152,22 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inflation Rate MoMDEC</t>
+          <t>Core Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>0.3%</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0.4%</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4182,26 +4182,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NY Empire State Manufacturing IndexJAN</t>
+          <t>Inflation Rate MoMDEC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>-12.60</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4582,26 +4582,18 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Export Prices MoMDEC</t>
+          <t>Philly Fed New OrdersJAN</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -4612,16 +4604,20 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexJAN</t>
+          <t>Retail Sales YoYDEC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>39.00</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
       <c r="F172" t="n">
         <v>3</v>
       </c>
@@ -4634,26 +4630,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/11</t>
+          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>217K</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>210K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>209.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -4664,22 +4660,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexJAN</t>
+          <t>Import Prices MoMDEC</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -4694,26 +4690,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMDEC</t>
+          <t>Jobless Claims 4-week AverageJAN/11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>212.75K</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -4724,26 +4716,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/04</t>
+          <t>Retail Sales MoMDEC</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>1859K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>1870K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1870.0K</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4754,16 +4746,20 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsJAN</t>
+          <t>Export Prices YoYDEC</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
       <c r="F177" t="n">
         <v>3</v>
       </c>
@@ -4776,24 +4772,16 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Import Prices YoYDEC</t>
+          <t>Philly Fed EmploymentJAN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>1.6%</t>
-        </is>
-      </c>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="n">
         <v>3</v>
       </c>
@@ -4806,16 +4794,24 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidJAN</t>
+          <t>Import Prices YoYDEC</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>31.90</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>1.6%</t>
+        </is>
+      </c>
       <c r="F179" t="n">
         <v>3</v>
       </c>
@@ -4828,12 +4824,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentJAN</t>
+          <t>Philly Fed Prices PaidJAN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>31.90</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -4850,20 +4846,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Export Prices YoYDEC</t>
+          <t>Philly Fed Business ConditionsJAN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="n">
         <v>3</v>
       </c>
@@ -4876,26 +4868,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Retail Sales MoMDEC</t>
+          <t>Continuing Jobless ClaimsJAN/04</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1859K</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>1870K</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1870.0K</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -4906,22 +4898,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/11</t>
+          <t>Retail Sales Ex Autos MoMDEC</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>212.75K</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184">
@@ -4932,22 +4928,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Import Prices MoMDEC</t>
+          <t>Philadelphia Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -4962,26 +4958,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMDEC</t>
+          <t>Initial Jobless ClaimsJAN/11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>217K</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>210K</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>209.0K</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -4992,20 +4988,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Retail Sales YoYDEC</t>
+          <t>Philly Fed CAPEX IndexJAN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="n">
         <v>3</v>
       </c>
@@ -5018,18 +5010,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersJAN</t>
+          <t>Export Prices MoMDEC</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="F187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -5378,22 +5378,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYDEC</t>
+          <t>Industrial Production MoMDEC</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -5404,22 +5408,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Manufacturing Production MoMDEC</t>
+          <t>Capacity UtilizationDEC</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -5434,18 +5438,18 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Industrial Production YoYDEC</t>
+          <t>Manufacturing Production YoYDEC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -5460,22 +5464,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Capacity UtilizationDEC</t>
+          <t>Manufacturing Production MoMDEC</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -5490,26 +5494,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Industrial Production MoMDEC</t>
+          <t>Industrial Production YoYDEC</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>4.165%</t>
+          <t>4.215%</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>4.215%</t>
+          <t>4.165%</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -6176,18 +6176,22 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
+          <t>EIA Gasoline Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.068M</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>2.332M</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2.5M</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
@@ -6198,22 +6202,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/17</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>-3.07M</t>
+          <t>-1.017M</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>0.6M</t>
+          <t>-2.1M</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -6224,12 +6228,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/17</t>
+          <t>15-Year Mortgage RateJAN/23</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>-0.043M</t>
+          <t>6.16%</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -6246,12 +6250,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>-0.148M</t>
+          <t>-0.473M</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -6268,12 +6272,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/17</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.184M</t>
+          <t>0.068M</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -6290,12 +6294,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/17</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>-0.473M</t>
+          <t>-0.148M</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -6312,12 +6316,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateJAN/23</t>
+          <t>EIA Gasoline Production ChangeJAN/17</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-0.043M</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -6334,22 +6338,22 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/17</t>
+          <t>EIA Distillate Stocks ChangeJAN/17</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>-1.017M</t>
+          <t>-3.07M</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-2.1M</t>
+          <t>0.6M</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -6360,22 +6364,18 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/17</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2.332M</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>2.5M</t>
-        </is>
-      </c>
+          <t>-1.125M</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/17</t>
+          <t>EIA Crude Oil Imports ChangeJAN/17</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>-1.125M</t>
+          <t>0.184M</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -6560,22 +6560,26 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMDEC</t>
+          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -6586,26 +6590,26 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalJAN</t>
+          <t>Existing Home SalesDEC</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>4.24M</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.19M</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>4.1M</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -6616,22 +6620,22 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalJAN</t>
+          <t>Michigan Current Conditions FinalJAN</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -6646,26 +6650,26 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalJAN</t>
+          <t>Michigan Consumer Sentiment FinalJAN</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -6676,26 +6680,26 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Existing Home SalesDEC</t>
+          <t>Michigan Consumer Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>4.24M</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>4.19M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>4.1M</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -6706,26 +6710,22 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalJAN</t>
+          <t>Existing Home Sales MoMDEC</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -6736,26 +6736,26 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalJAN</t>
+          <t>Michigan Inflation Expectations FinalJAN</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>4.195%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.195%</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -7342,18 +7342,22 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexJAN</t>
+          <t>Richmond Fed Manufacturing IndexJAN</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr"/>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -7368,22 +7372,26 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
+          <t>CB Consumer ConfidenceJAN</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>104.1</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>105.6</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -7394,26 +7402,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceJAN</t>
+          <t>Richmond Fed Manufacturing Shipments IndexJAN</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>104.1</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>105.6</t>
-        </is>
-      </c>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -7424,22 +7428,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexJAN</t>
+          <t>Richmond Fed Services Revenues IndexJAN</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -7620,18 +7620,18 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateJAN/24</t>
+          <t>MBA Purchase IndexJAN/24</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>7.02%</t>
+          <t>162.4</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexJAN/24</t>
+          <t>MBA Mortgage ApplicationsJAN/24</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>520.9</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexJAN/24</t>
+          <t>MBA Mortgage Refinance IndexJAN/24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>520.9</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -7686,18 +7686,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsJAN/24</t>
+          <t>MBA 30-Year Mortgage RateJAN/24</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>7.02%</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexJAN/24</t>
+          <t>MBA Mortgage Market IndexJAN/24</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>162.4</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.028M</t>
+          <t>0.326M</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>-0.333M</t>
+          <t>0.128M</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -7860,17 +7860,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/24</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2.957M</t>
+          <t>3.463M</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>1.5M</t>
+          <t>3.2M</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -7886,15 +7886,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/24</t>
+          <t>EIA Distillate Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.532M</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>-4.994M</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>-2.1M</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="n">
         <v>3</v>
@@ -7908,12 +7912,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/24</t>
+          <t>EIA Crude Oil Imports ChangeJAN/24</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>-0.044M</t>
+          <t>0.532M</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -7930,18 +7934,22 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Stocks ChangeJAN/24</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.326M</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>2.957M</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1.5M</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -7952,19 +7960,15 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/24</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/24</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>-4.994M</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>-2.1M</t>
-        </is>
-      </c>
+          <t>-0.333M</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="n">
         <v>3</v>
@@ -7978,22 +7982,18 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/24</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3.463M</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>3.2M</t>
-        </is>
-      </c>
+          <t>0.028M</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/24</t>
+          <t>EIA Gasoline Production ChangeJAN/24</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.128M</t>
+          <t>-0.044M</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -8096,18 +8096,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PCE Prices QoQ AdvQ4</t>
+          <t>Real Consumer Spending QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -8122,26 +8122,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsJAN/25</t>
+          <t>Jobless Claims 4-week AverageJAN/25</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>207K</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>220K</t>
-        </is>
-      </c>
+          <t>212.5K</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>228.0K</t>
+          <t>214.0K</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
@@ -8152,22 +8148,18 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsJAN/18</t>
+          <t>GDP Sales QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>1858K</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -8182,26 +8174,26 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>GDP Growth Rate QoQ AdvQ4</t>
+          <t>Core PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
           <t>2.3%</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314">
@@ -8212,22 +8204,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>GDP Price Index QoQ AdvQ4</t>
+          <t>Initial Jobless ClaimsJAN/25</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>207K</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>220K</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>228.0K</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -8242,26 +8234,26 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Core PCE Prices QoQ AdvQ4</t>
+          <t>GDP Growth Rate QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -8272,18 +8264,22 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageJAN/25</t>
+          <t>Continuing Jobless ClaimsJAN/18</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>212.5K</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
+          <t>1858K</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1890K</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>214.0K</t>
+          <t>1885.0K</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -8298,18 +8294,18 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Real Consumer Spending QoQ AdvQ4</t>
+          <t>PCE Prices QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -8324,22 +8320,26 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>GDP Sales QoQ AdvQ4</t>
+          <t>GDP Price Index QoQ AdvQ4</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>3.2%</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr"/>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
@@ -8542,22 +8542,18 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PCE Price Index MoMDEC</t>
+          <t>Employment Cost - Wages QoQQ4</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -8572,26 +8568,26 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Personal Income MoMDEC</t>
+          <t>Employment Cost Index QoQQ4</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -8602,26 +8598,26 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PCE Price Index YoYDEC</t>
+          <t>Personal Spending MoMDEC</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -8632,26 +8628,26 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Core PCE Price Index YoYDEC</t>
+          <t>Core PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -8662,20 +8658,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Employment Cost - Benefits QoQQ4</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>0.8%</t>
-        </is>
-      </c>
+          <t>Fed Bowman Speech</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr"/>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="E331" t="inlineStr"/>
       <c r="F331" t="n">
         <v>2</v>
       </c>
@@ -8688,26 +8676,26 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Core PCE Price Index MoMDEC</t>
+          <t>Core PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
@@ -8718,26 +8706,26 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Personal Spending MoMDEC</t>
+          <t>PCE Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334">
@@ -8748,14 +8736,26 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Fed Bowman Speech</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr"/>
-      <c r="D334" t="inlineStr"/>
-      <c r="E334" t="inlineStr"/>
+          <t>Personal Income MoMDEC</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="F334" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -8766,22 +8766,22 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Employment Cost Index QoQQ4</t>
+          <t>PCE Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Employment Cost - Wages QoQQ4</t>
+          <t>Employment Cost - Benefits QoQQ4</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -8930,22 +8930,26 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>ISM Manufacturing EmploymentJAN</t>
+          <t>ISM Manufacturing PricesJAN</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>54.9</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
@@ -8956,26 +8960,26 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PMIJAN</t>
+          <t>Construction Spending MoMDEC</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -8986,22 +8990,26 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>ISM Manufacturing New OrdersJAN</t>
+          <t>ISM Manufacturing PMIJAN</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>55.1</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -9012,26 +9020,22 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Construction Spending MoMDEC</t>
+          <t>ISM Manufacturing EmploymentJAN</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345">
@@ -9042,22 +9046,18 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ISM Manufacturing PricesJAN</t>
+          <t>ISM Manufacturing New OrdersJAN</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>54.9</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -9232,26 +9232,22 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>JOLTs Job OpeningsDEC</t>
+          <t>JOLTs Job QuitsDEC</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>7.6M</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>8M</t>
-        </is>
-      </c>
+          <t>3.197M</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>7.8M</t>
+          <t>3.1M</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -9262,26 +9258,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Factory Orders MoMDEC</t>
+          <t>Factory Orders ex TransportationDEC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -9292,22 +9284,26 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Factory Orders ex TransportationDEC</t>
+          <t>Factory Orders MoMDEC</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -9318,22 +9314,26 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>JOLTs Job QuitsDEC</t>
+          <t>JOLTs Job OpeningsDEC</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>3.197M</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>7.6M</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>3.1M</t>
+          <t>7.8M</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -9616,18 +9616,22 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ImportsDEC</t>
+          <t>Balance of TradeDEC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>$364.9B</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr"/>
+          <t>$-98.4B</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>$-96.6B</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>$ 355.0B</t>
+          <t>$ -93.0B</t>
         </is>
       </c>
       <c r="F370" t="n">
@@ -9642,14 +9646,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Treasury Refunding Announcement</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr"/>
+          <t>ExportsDEC</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>$266.5B</t>
+        </is>
+      </c>
       <c r="D371" t="inlineStr"/>
-      <c r="E371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>$ 262B</t>
+        </is>
+      </c>
       <c r="F371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="372">
@@ -9660,22 +9672,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ExportsDEC</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>$266.5B</t>
-        </is>
-      </c>
+          <t>Treasury Refunding Announcement</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>$ 262B</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="373">
@@ -9686,22 +9690,18 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Balance of TradeDEC</t>
+          <t>ImportsDEC</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>$-98.4B</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>$-96.6B</t>
-        </is>
-      </c>
+          <t>$364.9B</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>$ -93.0B</t>
+          <t>$ 355.0B</t>
         </is>
       </c>
       <c r="F373" t="n">
@@ -9928,15 +9928,19 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
+          <t>EIA Distillate Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.373M</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
+          <t>-5.471M</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-1.5M</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr"/>
       <c r="F382" t="n">
         <v>3</v>
@@ -9950,12 +9954,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
+          <t>EIA Crude Oil Imports ChangeJAN/31</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.16M</t>
+          <t>-0.178M</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -9972,12 +9976,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeJAN/31</t>
+          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>-0.027M</t>
+          <t>-0.186M</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -9994,17 +9998,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Gasoline Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>8.664M</t>
+          <t>2.233M</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2.6M</t>
+          <t>1.2M</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
@@ -10020,22 +10024,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeJAN/31</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2.233M</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>1.2M</t>
-        </is>
-      </c>
+          <t>-0.034M</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeJAN/31</t>
+          <t>EIA Gasoline Production ChangeJAN/31</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>-0.186M</t>
+          <t>-0.027M</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10068,12 +10068,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeJAN/31</t>
+          <t>EIA Heating Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>-0.178M</t>
+          <t>0.373M</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10090,18 +10090,22 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeJAN/31</t>
+          <t>EIA Crude Oil Stocks ChangeJAN/31</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>-0.034M</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
+          <t>8.664M</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2.6M</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -10112,19 +10116,15 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeJAN/31</t>
+          <t>EIA Refinery Crude Runs ChangeJAN/31</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>-5.471M</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>-1.5M</t>
-        </is>
-      </c>
+          <t>0.16M</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr"/>
       <c r="F390" t="n">
         <v>3</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/07</t>
+          <t>MBA Mortgage Market IndexFEB/07</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10396,14 +10396,14 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/07</t>
+          <t>MBA Mortgage Refinance IndexFEB/07</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr"/>
       <c r="F404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
@@ -10414,14 +10414,14 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/07</t>
+          <t>MBA 30-Year Mortgage RateFEB/07</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr"/>
       <c r="F405" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="406">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/07</t>
+          <t>MBA Mortgage ApplicationsFEB/07</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/07</t>
+          <t>MBA Purchase IndexFEB/07</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/07</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -10638,14 +10638,14 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -10656,14 +10656,14 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/07</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Production ChangeFEB/07</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -10692,14 +10692,14 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/07</t>
+          <t>EIA Gasoline Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -10710,14 +10710,14 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/07</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/07</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/07</t>
+          <t>EIA Distillate Stocks ChangeFEB/07</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -10880,14 +10880,14 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>PPIJAN</t>
+          <t>Jobless Claims 4-week AverageFEB/08</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>216.0K</t>
         </is>
       </c>
       <c r="F428" t="n">
@@ -10902,14 +10902,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
+          <t>Core PPI YoYJAN</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F429" t="n">
@@ -10924,22 +10928,18 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Core PPI MoMJAN</t>
+          <t>Continuing Jobless ClaimsFEB/01</t>
         </is>
       </c>
       <c r="C430" t="inlineStr"/>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1875.0K</t>
         </is>
       </c>
       <c r="F430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -10950,18 +10950,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>PPI YoYJAN</t>
+          <t>PPI MoMJAN</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -10972,22 +10976,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
+          <t>Initial Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>216K</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>215.0K</t>
         </is>
       </c>
       <c r="F432" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433">
@@ -10998,22 +11002,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/08</t>
+          <t>PPI Ex Food, Energy and Trade YoYJAN</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>216K</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>215.0K</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F433" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -11024,22 +11028,18 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PPI MoMJAN</t>
+          <t>PPI YoYJAN</t>
         </is>
       </c>
       <c r="C434" t="inlineStr"/>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+      <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -11050,18 +11050,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/01</t>
+          <t>Core PPI MoMJAN</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>1875.0K</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -11072,18 +11076,14 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Core PPI YoYJAN</t>
+          <t>PPI Ex Food, Energy and Trade MoMJAN</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F436" t="n">
@@ -11098,14 +11098,14 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/08</t>
+          <t>PPIJAN</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>216.0K</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="F437" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -11478,22 +11478,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Industrial Production MoMJAN</t>
+          <t>Industrial Production YoYJAN</t>
         </is>
       </c>
       <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
+      <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F455" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -11504,18 +11500,14 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Capacity UtilizationJAN</t>
+          <t>Manufacturing Production YoYJAN</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>77.7%</t>
-        </is>
-      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F456" t="n">
@@ -11556,14 +11548,18 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Manufacturing Production YoYJAN</t>
+          <t>Capacity UtilizationJAN</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F458" t="n">
@@ -11578,18 +11574,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Industrial Production YoYJAN</t>
+          <t>Industrial Production MoMJAN</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -12098,14 +12098,14 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Fed Barr Speech</t>
+          <t>52-Week Bill Auction</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="486">
@@ -12134,14 +12134,14 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>52-Week Bill Auction</t>
+          <t>Fed Barr Speech</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="488">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Overall Net Capital FlowsDEC</t>
+          <t>Foreign Bond InvestmentDEC</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
@@ -12170,14 +12170,18 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Foreign Bond InvestmentDEC</t>
+          <t>Net Long-term TIC FlowsDEC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>$149.1B</t>
+        </is>
+      </c>
       <c r="E489" t="inlineStr"/>
       <c r="F489" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -12188,18 +12192,14 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Net Long-term TIC FlowsDEC</t>
+          <t>Overall Net Capital FlowsDEC</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>$149.1B</t>
-        </is>
-      </c>
+      <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr"/>
       <c r="F490" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -12304,14 +12304,14 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA 30-Year Mortgage RateFEB/14</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -12358,14 +12358,14 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr"/>
       <c r="F499" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
@@ -12566,18 +12566,18 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits PrelJAN</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr">
         <is>
-          <t>1.39M</t>
+          <t>1.45M</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>1.47M</t>
         </is>
       </c>
       <c r="F509" t="n">
@@ -12592,22 +12592,18 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Building Permits PrelJAN</t>
+          <t>Housing Starts MoMJAN</t>
         </is>
       </c>
       <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>1.45M</t>
-        </is>
-      </c>
+      <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>1.47M</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="F510" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="511">
@@ -12618,18 +12614,22 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Housing Starts MoMJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
@@ -12900,22 +12900,14 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E526" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr"/>
       <c r="F526" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="527">
@@ -12926,22 +12918,14 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E527" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D527" t="inlineStr"/>
+      <c r="E527" t="inlineStr"/>
       <c r="F527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -12974,7 +12958,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -12992,12 +12976,16 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr"/>
-      <c r="E530" t="inlineStr"/>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F530" t="n">
         <v>3</v>
       </c>
@@ -13010,14 +12998,22 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F531" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="532">
@@ -13028,14 +13024,22 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F532" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533">
@@ -13046,16 +13050,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageFEB/15</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="inlineStr"/>
-      <c r="E533" t="inlineStr">
-        <is>
-          <t>219.0K</t>
-        </is>
-      </c>
+      <c r="E533" t="inlineStr"/>
       <c r="F533" t="n">
         <v>3</v>
       </c>
@@ -13068,16 +13068,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E534" t="inlineStr"/>
       <c r="F534" t="n">
         <v>3</v>
       </c>
@@ -13090,12 +13086,16 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F535" t="n">
         <v>3</v>
       </c>
@@ -13108,12 +13108,16 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Jobless Claims 4-week AverageFEB/15</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>219.0K</t>
+        </is>
+      </c>
       <c r="F536" t="n">
         <v>3</v>
       </c>
@@ -13126,22 +13130,14 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E537" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="inlineStr"/>
       <c r="F537" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -13152,14 +13148,22 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>220.0K</t>
+        </is>
+      </c>
       <c r="F538" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="539">
@@ -13170,7 +13174,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -13188,22 +13192,14 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D540" t="inlineStr"/>
+      <c r="E540" t="inlineStr"/>
       <c r="F540" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -13214,14 +13210,22 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Philly Fed CAPEX IndexFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F541" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
@@ -13232,16 +13236,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Philly Fed CAPEX IndexFEB</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr">
-        <is>
-          <t>1879.0K</t>
-        </is>
-      </c>
+      <c r="E542" t="inlineStr"/>
       <c r="F542" t="n">
         <v>3</v>
       </c>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -13468,14 +13468,14 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr"/>
       <c r="E554" t="inlineStr"/>
       <c r="F554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="555">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -13504,14 +13504,14 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr"/>
       <c r="E556" t="inlineStr"/>
       <c r="F556" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="557">
@@ -13522,14 +13522,14 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
       <c r="D557" t="inlineStr"/>
       <c r="E557" t="inlineStr"/>
       <c r="F557" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -13540,14 +13540,14 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr"/>
       <c r="F558" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -13558,14 +13558,14 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr"/>
       <c r="E559" t="inlineStr"/>
       <c r="F559" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="560">
@@ -13576,14 +13576,14 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr"/>
       <c r="F560" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="561">
@@ -13594,14 +13594,14 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr"/>
       <c r="F561" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="562">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>EIA Gasoline Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -13666,14 +13666,14 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr"/>
       <c r="E565" t="inlineStr"/>
       <c r="F565" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="566">
@@ -13684,14 +13684,14 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>EIA Gasoline Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr"/>
       <c r="F566" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="567">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
+          <t>15-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -13738,14 +13738,14 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/14</t>
+          <t>EIA Crude Oil Imports ChangeFEB/14</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr"/>
       <c r="E569" t="inlineStr"/>
       <c r="F569" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateFEB/20</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
+          <t>30-Year Mortgage RateFEB/20</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/14</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/14</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/14</t>
+          <t>EIA Distillate Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/14</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/14</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -13864,7 +13864,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateFEB/20</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/14</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -14062,18 +14062,14 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
+      <c r="D587" t="inlineStr"/>
       <c r="E587" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F587" t="n">
@@ -14088,11 +14084,15 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Services PMI FlashFEB</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
           <t>52.7</t>
@@ -14110,14 +14110,14 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr"/>
       <c r="E589" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F589" t="n">
@@ -14132,14 +14132,14 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
+          <t>S&amp;P Global Composite PMI FlashFEB</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr"/>
       <c r="E590" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="F590" t="n">
@@ -14180,14 +14180,14 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashFEB</t>
+          <t>S&amp;P Global Manufacturing PMI FlashFEB</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr"/>
       <c r="E592" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="F592" t="n">
@@ -14202,18 +14202,18 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Michigan Inflation Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F593" t="n">
@@ -14228,18 +14228,18 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F594" t="n">
@@ -14254,22 +14254,22 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F595" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="596">
@@ -14280,22 +14280,18 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Existing Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
+      <c r="D596" t="inlineStr"/>
       <c r="E596" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F596" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="597">
@@ -14306,22 +14302,22 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Existing Home SalesJAN</t>
         </is>
       </c>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.17M</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>4.16M</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="598">
@@ -14332,18 +14328,22 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMJAN</t>
+          <t>Michigan Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C598" t="inlineStr"/>
-      <c r="D598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -14354,22 +14354,22 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Existing Home SalesJAN</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>4.17M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>4.16M</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F599" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -14380,18 +14380,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Michigan Consumer Expectations FinalFEB</t>
+          <t>Michigan Current Conditions FinalFEB</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F600" t="n">
@@ -14406,22 +14406,22 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
+          <t>Michigan Consumer Sentiment FinalFEB</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F601" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602">
@@ -14432,18 +14432,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Michigan Current Conditions FinalFEB</t>
+          <t>Michigan Consumer Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -14458,22 +14458,22 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Michigan Consumer Sentiment FinalFEB</t>
+          <t>Michigan 5 Year Inflation Expectations FinalFEB</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountFEB/21</t>
+          <t>Baker Hughes Oil Rig CountFEB/21</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountFEB/21</t>
+          <t>Baker Hughes Total Rigs CountFEB/21</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C619" t="inlineStr"/>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
@@ -14900,7 +14900,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
@@ -14936,18 +14936,14 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price IndexDEC</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr"/>
-      <c r="E628" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E628" t="inlineStr"/>
       <c r="F628" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="629">
@@ -14958,18 +14954,14 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
       <c r="D629" t="inlineStr"/>
-      <c r="E629" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E629" t="inlineStr"/>
       <c r="F629" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="630">
@@ -14998,14 +14990,18 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr"/>
-      <c r="E631" t="inlineStr"/>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F631" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="632">
@@ -15016,7 +15012,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -15034,7 +15030,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -15052,14 +15048,18 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>House Price IndexDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
       <c r="D634" t="inlineStr"/>
-      <c r="E634" t="inlineStr"/>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F634" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635">
@@ -15070,14 +15070,14 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="inlineStr"/>
       <c r="E635" t="inlineStr"/>
       <c r="F635" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="636">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
@@ -15142,14 +15142,14 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
       <c r="D639" t="inlineStr"/>
       <c r="E639" t="inlineStr"/>
       <c r="F639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="640">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -15394,14 +15394,14 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr"/>
       <c r="E653" t="inlineStr"/>
       <c r="F653" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="654">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA Mortgage ApplicationsFEB/21</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -15430,14 +15430,14 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateFEB/21</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
       <c r="D655" t="inlineStr"/>
       <c r="E655" t="inlineStr"/>
       <c r="F655" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="656">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>MBA Mortgage Refinance IndexFEB/21</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>MBA Purchase IndexFEB/21</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -15538,14 +15538,14 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr"/>
       <c r="E661" t="inlineStr"/>
       <c r="F661" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="662">
@@ -15556,14 +15556,14 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/21</t>
+          <t>MBA 30-Year Mortgage RateFEB/21</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr"/>
       <c r="E662" t="inlineStr"/>
       <c r="F662" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="663">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/21</t>
+          <t>MBA Mortgage Market IndexFEB/21</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>New Home SalesJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>New Home Sales MoMJAN</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>New Home Sales MoMJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>New Home SalesJAN</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -15754,14 +15754,14 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr"/>
       <c r="E673" t="inlineStr"/>
       <c r="F673" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="674">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -15808,7 +15808,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -15844,14 +15844,14 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr"/>
       <c r="E678" t="inlineStr"/>
       <c r="F678" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="679">
@@ -15862,14 +15862,14 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr"/>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="680">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -15916,14 +15916,14 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="inlineStr"/>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="683">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
+          <t>EIA Crude Oil Imports ChangeFEB/21</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeFEB/21</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeFEB/21</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Building Permits MoM FinalJAN</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeFEB/21</t>
+          <t>EIA Distillate Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeFEB/21</t>
+          <t>EIA Heating Oil Stocks ChangeFEB/21</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
       <c r="D689" t="inlineStr"/>
       <c r="E689" t="inlineStr"/>
       <c r="F689" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="690">
@@ -16060,14 +16060,14 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeFEB/21</t>
+          <t>EIA Gasoline Production ChangeFEB/21</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
       <c r="D690" t="inlineStr"/>
       <c r="E690" t="inlineStr"/>
       <c r="F690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="691">
@@ -16091,19 +16091,19 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2025-02-26 22:30:00+05:30</t>
+          <t>2025-02-26 22:00:00+05:30</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr"/>
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="693">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Building Permits FinalJAN</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalJAN</t>
+          <t>Building Permits FinalJAN</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
@@ -16142,6 +16142,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2025-02-26 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr"/>
+      <c r="D695" t="inlineStr"/>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2025-02-26 22:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Fed Bostic Speech</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr"/>
+      <c r="D696" t="inlineStr"/>
+      <c r="E696" t="inlineStr"/>
+      <c r="F696" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2025-02-26 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Building Permits FinalJAN</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr"/>
+      <c r="D697" t="inlineStr"/>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2025-02-26 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>2-Year FRN Auction</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr"/>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2025-02-26 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>7-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr"/>
+      <c r="D699" t="inlineStr"/>
+      <c r="E699" t="inlineStr"/>
+      <c r="F699" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2025-02-26 23:30:00+05:30</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Building Permits MoM FinalJAN</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr"/>
+      <c r="D700" t="inlineStr"/>
+      <c r="E700" t="inlineStr"/>
+      <c r="F700" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
